--- a/artfynd/A 18713-2026 artfynd.xlsx
+++ b/artfynd/A 18713-2026 artfynd.xlsx
@@ -772,40 +772,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133590069</v>
+        <v>133590299</v>
       </c>
       <c r="B3" t="n">
-        <v>93257</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -814,13 +818,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472151</v>
+        <v>472075</v>
       </c>
       <c r="R3" t="n">
-        <v>6716422</v>
+        <v>6716793</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +854,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133591484</v>
+        <v>133590549</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472362</v>
+        <v>472261</v>
       </c>
       <c r="R4" t="n">
-        <v>6716594</v>
+        <v>6716776</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133590549</v>
+        <v>133591484</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472261</v>
+        <v>472362</v>
       </c>
       <c r="R5" t="n">
-        <v>6716776</v>
+        <v>6716594</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,45 +1083,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133590299</v>
+        <v>133592266</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1130,13 +1126,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472075</v>
+        <v>472407</v>
       </c>
       <c r="R6" t="n">
-        <v>6716793</v>
+        <v>6716410</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133592266</v>
+        <v>133590069</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>93257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,31 +1300,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1337,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472407</v>
+        <v>472151</v>
       </c>
       <c r="R8" t="n">
-        <v>6716410</v>
+        <v>6716422</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1375,12 +1369,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från 2025</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1399,46 +1399,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133589310</v>
+        <v>133590302</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1446,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472603</v>
+        <v>472041</v>
       </c>
       <c r="R9" t="n">
-        <v>6716357</v>
+        <v>6716845</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1476,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133590160</v>
+        <v>133590494</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,31 +1511,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472090</v>
+        <v>472235</v>
       </c>
       <c r="R10" t="n">
-        <v>6716542</v>
+        <v>6716801</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1590,17 +1576,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1619,43 +1601,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133592241</v>
+        <v>133589761</v>
       </c>
       <c r="B11" t="n">
-        <v>8460</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1663,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472390</v>
+        <v>472217</v>
       </c>
       <c r="R11" t="n">
-        <v>6716412</v>
+        <v>6716274</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1726,7 +1702,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133589761</v>
+        <v>133589484</v>
       </c>
       <c r="B12" t="n">
         <v>79116</v>
@@ -1764,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472217</v>
+        <v>472324</v>
       </c>
       <c r="R12" t="n">
-        <v>6716274</v>
+        <v>6716197</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,37 +1803,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133589484</v>
+        <v>133589310</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>99181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1865,13 +1850,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472324</v>
+        <v>472603</v>
       </c>
       <c r="R13" t="n">
-        <v>6716197</v>
+        <v>6716357</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1928,37 +1913,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133590302</v>
+        <v>133592241</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1966,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472041</v>
+        <v>472390</v>
       </c>
       <c r="R14" t="n">
-        <v>6716845</v>
+        <v>6716412</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2029,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133590494</v>
+        <v>133590160</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,26 +2031,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472235</v>
+        <v>472090</v>
       </c>
       <c r="R15" t="n">
-        <v>6716801</v>
+        <v>6716542</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2105,13 +2101,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133589122</v>
+        <v>133589866</v>
       </c>
       <c r="B16" t="n">
         <v>79359</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472506</v>
+        <v>472324</v>
       </c>
       <c r="R16" t="n">
-        <v>6716256</v>
+        <v>6716331</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133590542</v>
+        <v>133589122</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472247</v>
+        <v>472506</v>
       </c>
       <c r="R17" t="n">
-        <v>6716770</v>
+        <v>6716256</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133589139</v>
+        <v>133590542</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472522</v>
+        <v>472247</v>
       </c>
       <c r="R18" t="n">
-        <v>6716305</v>
+        <v>6716770</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133589866</v>
+        <v>133589139</v>
       </c>
       <c r="B19" t="n">
         <v>79359</v>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472324</v>
+        <v>472522</v>
       </c>
       <c r="R19" t="n">
-        <v>6716331</v>
+        <v>6716305</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,44 +2534,36 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133591800</v>
+        <v>133591270</v>
       </c>
       <c r="B20" t="n">
-        <v>93257</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2580,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472447</v>
+        <v>472362</v>
       </c>
       <c r="R20" t="n">
-        <v>6716555</v>
+        <v>6716669</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2616,11 +2608,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,7 +2635,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133592104</v>
+        <v>133591517</v>
       </c>
       <c r="B21" t="n">
         <v>79359</v>
@@ -2686,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472402</v>
+        <v>472342</v>
       </c>
       <c r="R21" t="n">
-        <v>6716474</v>
+        <v>6716578</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2749,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133591252</v>
+        <v>133590308</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,21 +2747,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2787,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472357</v>
+        <v>472127</v>
       </c>
       <c r="R22" t="n">
-        <v>6716679</v>
+        <v>6716842</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2850,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133591270</v>
+        <v>133591252</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2861,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2888,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472362</v>
+        <v>472357</v>
       </c>
       <c r="R23" t="n">
-        <v>6716669</v>
+        <v>6716679</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2951,7 +2938,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133591517</v>
+        <v>133592104</v>
       </c>
       <c r="B24" t="n">
         <v>79359</v>
@@ -2989,10 +2976,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472342</v>
+        <v>472402</v>
       </c>
       <c r="R24" t="n">
-        <v>6716578</v>
+        <v>6716474</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3052,36 +3039,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133590308</v>
+        <v>133591800</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>93257</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3090,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472127</v>
+        <v>472447</v>
       </c>
       <c r="R25" t="n">
-        <v>6716842</v>
+        <v>6716555</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3126,6 +3121,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,7 +3256,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133589936</v>
+        <v>133590144</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472164</v>
+        <v>472119</v>
       </c>
       <c r="R27" t="n">
-        <v>6716349</v>
+        <v>6716583</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133590144</v>
+        <v>133592147</v>
       </c>
       <c r="B29" t="n">
         <v>79359</v>
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472119</v>
+        <v>472401</v>
       </c>
       <c r="R29" t="n">
-        <v>6716583</v>
+        <v>6716444</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133592147</v>
+        <v>133589936</v>
       </c>
       <c r="B30" t="n">
         <v>79359</v>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472401</v>
+        <v>472164</v>
       </c>
       <c r="R30" t="n">
-        <v>6716444</v>
+        <v>6716349</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133589911</v>
+        <v>133589958</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472198</v>
+        <v>472167</v>
       </c>
       <c r="R32" t="n">
-        <v>6716371</v>
+        <v>6716325</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3963,44 +3963,36 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133590442</v>
+        <v>133590674</v>
       </c>
       <c r="B34" t="n">
-        <v>93257</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4009,13 +4001,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472208</v>
+        <v>472291</v>
       </c>
       <c r="R34" t="n">
-        <v>6716811</v>
+        <v>6716730</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4045,11 +4037,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4077,10 +4064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133589958</v>
+        <v>133589886</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4088,21 +4075,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4115,13 +4102,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472167</v>
+        <v>472246</v>
       </c>
       <c r="R35" t="n">
-        <v>6716325</v>
+        <v>6716353</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133590082</v>
+        <v>133590442</v>
       </c>
       <c r="B36" t="n">
-        <v>8460</v>
+        <v>93257</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4189,32 +4176,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4222,10 +4211,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472135</v>
+        <v>472208</v>
       </c>
       <c r="R36" t="n">
-        <v>6716430</v>
+        <v>6716811</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4258,6 +4247,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4285,7 +4279,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133592130</v>
+        <v>133589911</v>
       </c>
       <c r="B37" t="n">
         <v>79359</v>
@@ -4323,10 +4317,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472414</v>
+        <v>472198</v>
       </c>
       <c r="R37" t="n">
-        <v>6716446</v>
+        <v>6716371</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4386,37 +4380,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133590674</v>
+        <v>133590082</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>8460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472291</v>
+        <v>472135</v>
       </c>
       <c r="R38" t="n">
-        <v>6716730</v>
+        <v>6716430</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133589886</v>
+        <v>133592130</v>
       </c>
       <c r="B39" t="n">
         <v>79359</v>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472246</v>
+        <v>472414</v>
       </c>
       <c r="R39" t="n">
-        <v>6716353</v>
+        <v>6716446</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133592159</v>
+        <v>133591503</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4599,21 +4599,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472404</v>
+        <v>472348</v>
       </c>
       <c r="R40" t="n">
-        <v>6716455</v>
+        <v>6716596</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133589898</v>
+        <v>133592159</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4828,13 +4828,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472233</v>
+        <v>472404</v>
       </c>
       <c r="R42" t="n">
-        <v>6716352</v>
+        <v>6716455</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4891,37 +4891,43 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133591503</v>
+        <v>133590255</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4929,13 +4935,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472348</v>
+        <v>472087</v>
       </c>
       <c r="R43" t="n">
-        <v>6716596</v>
+        <v>6716742</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4992,43 +4998,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133590255</v>
+        <v>133589898</v>
       </c>
       <c r="B44" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472087</v>
+        <v>472233</v>
       </c>
       <c r="R44" t="n">
-        <v>6716742</v>
+        <v>6716352</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133589949</v>
+        <v>133590561</v>
       </c>
       <c r="B45" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472174</v>
+        <v>472249</v>
       </c>
       <c r="R45" t="n">
-        <v>6716377</v>
+        <v>6716778</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133589715</v>
+        <v>133590454</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,13 +5238,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472246</v>
+        <v>472220</v>
       </c>
       <c r="R46" t="n">
-        <v>6716249</v>
+        <v>6716814</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133590561</v>
+        <v>133589839</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472249</v>
+        <v>472288</v>
       </c>
       <c r="R47" t="n">
-        <v>6716778</v>
+        <v>6716309</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133589832</v>
+        <v>133590570</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5413,31 +5413,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472206</v>
+        <v>472257</v>
       </c>
       <c r="R48" t="n">
-        <v>6716317</v>
+        <v>6716771</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5483,17 +5478,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5512,7 +5503,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133589839</v>
+        <v>133589949</v>
       </c>
       <c r="B49" t="n">
         <v>79359</v>
@@ -5550,13 +5541,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472288</v>
+        <v>472174</v>
       </c>
       <c r="R49" t="n">
-        <v>6716309</v>
+        <v>6716377</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5613,10 +5604,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133590570</v>
+        <v>133589715</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5624,21 +5615,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5651,10 +5642,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472257</v>
+        <v>472246</v>
       </c>
       <c r="R50" t="n">
-        <v>6716771</v>
+        <v>6716249</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5714,10 +5705,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133590454</v>
+        <v>133589832</v>
       </c>
       <c r="B51" t="n">
-        <v>79117</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,26 +5716,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5752,13 +5748,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472220</v>
+        <v>472206</v>
       </c>
       <c r="R51" t="n">
-        <v>6716814</v>
+        <v>6716317</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5790,13 +5786,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133589789</v>
+        <v>133589660</v>
       </c>
       <c r="B53" t="n">
         <v>79359</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>472223</v>
+        <v>472264</v>
       </c>
       <c r="R53" t="n">
-        <v>6716268</v>
+        <v>6716238</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6017,42 +6017,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133591871</v>
+        <v>133589789</v>
       </c>
       <c r="B54" t="n">
-        <v>57162</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6060,10 +6055,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>472421</v>
+        <v>472223</v>
       </c>
       <c r="R54" t="n">
-        <v>6716519</v>
+        <v>6716268</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6104,6 +6099,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6122,7 +6118,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133589660</v>
+        <v>133592299</v>
       </c>
       <c r="B55" t="n">
         <v>79359</v>
@@ -6160,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>472264</v>
+        <v>472393</v>
       </c>
       <c r="R55" t="n">
-        <v>6716238</v>
+        <v>6716395</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6223,37 +6219,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133590101</v>
+        <v>133591871</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6261,10 +6262,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>472128</v>
+        <v>472421</v>
       </c>
       <c r="R56" t="n">
-        <v>6716533</v>
+        <v>6716519</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6305,7 +6306,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133592299</v>
+        <v>133590101</v>
       </c>
       <c r="B57" t="n">
         <v>79359</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>472393</v>
+        <v>472128</v>
       </c>
       <c r="R57" t="n">
-        <v>6716395</v>
+        <v>6716533</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133589587</v>
+        <v>133589557</v>
       </c>
       <c r="B59" t="n">
         <v>79359</v>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>472365</v>
+        <v>472355</v>
       </c>
       <c r="R59" t="n">
-        <v>6716324</v>
+        <v>6716306</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133589557</v>
+        <v>133589587</v>
       </c>
       <c r="B60" t="n">
         <v>79359</v>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>472355</v>
+        <v>472365</v>
       </c>
       <c r="R60" t="n">
-        <v>6716306</v>
+        <v>6716324</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6732,7 +6732,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133589426</v>
+        <v>133590189</v>
       </c>
       <c r="B61" t="n">
         <v>79359</v>
@@ -6770,13 +6770,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>472436</v>
+        <v>472100</v>
       </c>
       <c r="R61" t="n">
-        <v>6716208</v>
+        <v>6716639</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,10 +6833,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133589201</v>
+        <v>133590240</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6844,21 +6844,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>472581</v>
+        <v>472083</v>
       </c>
       <c r="R62" t="n">
-        <v>6716345</v>
+        <v>6716723</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6934,7 +6934,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133590405</v>
+        <v>133590417</v>
       </c>
       <c r="B63" t="n">
         <v>79116</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>472190</v>
+        <v>472173</v>
       </c>
       <c r="R63" t="n">
-        <v>6716830</v>
+        <v>6716842</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133590189</v>
+        <v>133590624</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>472100</v>
+        <v>472263</v>
       </c>
       <c r="R64" t="n">
-        <v>6716639</v>
+        <v>6716734</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133590319</v>
+        <v>133590405</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7147,21 +7147,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472145</v>
+        <v>472190</v>
       </c>
       <c r="R65" t="n">
-        <v>6716826</v>
+        <v>6716830</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7237,42 +7237,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133592346</v>
+        <v>133590028</v>
       </c>
       <c r="B66" t="n">
-        <v>57162</v>
+        <v>79117</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7280,13 +7275,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472396</v>
+        <v>472152</v>
       </c>
       <c r="R66" t="n">
-        <v>6716339</v>
+        <v>6716346</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7318,17 +7313,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Betad tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7347,10 +7338,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133590240</v>
+        <v>133590319</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7358,21 +7349,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7385,13 +7376,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472083</v>
+        <v>472145</v>
       </c>
       <c r="R67" t="n">
-        <v>6716723</v>
+        <v>6716826</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7448,10 +7439,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133591819</v>
+        <v>133589201</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7459,21 +7450,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7486,13 +7477,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472431</v>
+        <v>472581</v>
       </c>
       <c r="R68" t="n">
-        <v>6716531</v>
+        <v>6716345</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7516,12 +7507,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7549,7 +7540,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133589444</v>
+        <v>133591819</v>
       </c>
       <c r="B69" t="n">
         <v>79116</v>
@@ -7587,13 +7578,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472312</v>
+        <v>472431</v>
       </c>
       <c r="R69" t="n">
-        <v>6716221</v>
+        <v>6716531</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7617,12 +7608,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7650,10 +7641,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133590417</v>
+        <v>133589426</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7661,21 +7652,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7688,13 +7679,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472173</v>
+        <v>472436</v>
       </c>
       <c r="R70" t="n">
-        <v>6716842</v>
+        <v>6716208</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7718,12 +7709,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7751,7 +7742,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133589629</v>
+        <v>133589444</v>
       </c>
       <c r="B71" t="n">
         <v>79116</v>
@@ -7789,10 +7780,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472318</v>
+        <v>472312</v>
       </c>
       <c r="R71" t="n">
-        <v>6716281</v>
+        <v>6716221</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7852,10 +7843,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133589542</v>
+        <v>133589629</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>79116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7863,31 +7854,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7895,10 +7881,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472359</v>
+        <v>472318</v>
       </c>
       <c r="R72" t="n">
-        <v>6716287</v>
+        <v>6716281</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7933,17 +7919,13 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7962,37 +7944,42 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133590624</v>
+        <v>133592346</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>57162</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8000,10 +7987,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472263</v>
+        <v>472396</v>
       </c>
       <c r="R73" t="n">
-        <v>6716734</v>
+        <v>6716339</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8038,13 +8025,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Betad tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8063,10 +8054,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133590028</v>
+        <v>133589542</v>
       </c>
       <c r="B74" t="n">
-        <v>79117</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8074,26 +8065,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8101,10 +8097,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472152</v>
+        <v>472359</v>
       </c>
       <c r="R74" t="n">
-        <v>6716346</v>
+        <v>6716287</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8131,12 +8127,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8145,7 +8146,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8164,7 +8164,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133590202</v>
+        <v>133590498</v>
       </c>
       <c r="B75" t="n">
         <v>79359</v>
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472083</v>
+        <v>472251</v>
       </c>
       <c r="R75" t="n">
-        <v>6716615</v>
+        <v>6716795</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8265,10 +8265,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133590498</v>
+        <v>133590038</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472251</v>
+        <v>472157</v>
       </c>
       <c r="R76" t="n">
-        <v>6716795</v>
+        <v>6716343</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133590038</v>
+        <v>133590202</v>
       </c>
       <c r="B78" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8478,21 +8478,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8505,13 +8505,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472157</v>
+        <v>472083</v>
       </c>
       <c r="R78" t="n">
-        <v>6716343</v>
+        <v>6716615</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133591463</v>
+        <v>133589849</v>
       </c>
       <c r="B80" t="n">
         <v>79359</v>
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>472372</v>
+        <v>472309</v>
       </c>
       <c r="R80" t="n">
-        <v>6716600</v>
+        <v>6716305</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133591528</v>
+        <v>133590053</v>
       </c>
       <c r="B81" t="n">
         <v>79359</v>
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472337</v>
+        <v>472187</v>
       </c>
       <c r="R81" t="n">
-        <v>6716585</v>
+        <v>6716406</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133590113</v>
+        <v>133591463</v>
       </c>
       <c r="B82" t="n">
         <v>79359</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>472116</v>
+        <v>472372</v>
       </c>
       <c r="R82" t="n">
-        <v>6716545</v>
+        <v>6716600</v>
       </c>
       <c r="S82" t="n">
         <v>50</v>
@@ -8981,7 +8981,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133589849</v>
+        <v>133589470</v>
       </c>
       <c r="B83" t="n">
         <v>79359</v>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>472309</v>
+        <v>472321</v>
       </c>
       <c r="R83" t="n">
-        <v>6716305</v>
+        <v>6716236</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9082,7 +9082,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133589470</v>
+        <v>133589858</v>
       </c>
       <c r="B84" t="n">
         <v>79359</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>472321</v>
+        <v>472330</v>
       </c>
       <c r="R84" t="n">
-        <v>6716236</v>
+        <v>6716313</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9183,7 +9183,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133590053</v>
+        <v>133590229</v>
       </c>
       <c r="B85" t="n">
         <v>79359</v>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>472187</v>
+        <v>472048</v>
       </c>
       <c r="R85" t="n">
-        <v>6716406</v>
+        <v>6716642</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133590135</v>
+        <v>133590113</v>
       </c>
       <c r="B86" t="n">
         <v>79359</v>
@@ -9322,13 +9322,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>472107</v>
+        <v>472116</v>
       </c>
       <c r="R86" t="n">
-        <v>6716575</v>
+        <v>6716545</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133589365</v>
+        <v>133590135</v>
       </c>
       <c r="B87" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9396,31 +9396,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9428,13 +9423,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>472559</v>
+        <v>472107</v>
       </c>
       <c r="R87" t="n">
-        <v>6716299</v>
+        <v>6716575</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9458,17 +9453,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9477,6 +9467,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9495,7 +9486,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133590229</v>
+        <v>133591528</v>
       </c>
       <c r="B88" t="n">
         <v>79359</v>
@@ -9533,10 +9524,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>472048</v>
+        <v>472337</v>
       </c>
       <c r="R88" t="n">
-        <v>6716642</v>
+        <v>6716585</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -9596,45 +9587,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133592016</v>
+        <v>133589365</v>
       </c>
       <c r="B89" t="n">
-        <v>93257</v>
+        <v>57975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9642,10 +9630,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>472439</v>
+        <v>472559</v>
       </c>
       <c r="R89" t="n">
-        <v>6716486</v>
+        <v>6716299</v>
       </c>
       <c r="S89" t="n">
         <v>50</v>
@@ -9672,17 +9660,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Från 2025</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9691,7 +9679,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9710,42 +9697,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133590391</v>
+        <v>133592016</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>93257</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9753,10 +9743,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>472175</v>
+        <v>472439</v>
       </c>
       <c r="R90" t="n">
-        <v>6716830</v>
+        <v>6716486</v>
       </c>
       <c r="S90" t="n">
         <v>50</v>
@@ -9793,7 +9783,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9802,6 +9792,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9820,10 +9811,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133589858</v>
+        <v>133590391</v>
       </c>
       <c r="B91" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9831,26 +9822,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -9858,13 +9854,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472330</v>
+        <v>472175</v>
       </c>
       <c r="R91" t="n">
-        <v>6716313</v>
+        <v>6716830</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9896,13 +9892,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9921,44 +9921,36 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133591328</v>
+        <v>133590286</v>
       </c>
       <c r="B92" t="n">
-        <v>93257</v>
+        <v>79359</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -9967,10 +9959,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>472372</v>
+        <v>472056</v>
       </c>
       <c r="R92" t="n">
-        <v>6716649</v>
+        <v>6716776</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10003,11 +9995,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10035,10 +10022,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133592323</v>
+        <v>133591302</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10046,31 +10033,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10078,10 +10060,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472392</v>
+        <v>472353</v>
       </c>
       <c r="R93" t="n">
-        <v>6716353</v>
+        <v>6716653</v>
       </c>
       <c r="S93" t="n">
         <v>50</v>
@@ -10116,17 +10098,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10123,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133591603</v>
+        <v>133590752</v>
       </c>
       <c r="B94" t="n">
-        <v>91981</v>
+        <v>79117</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10156,33 +10134,25 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -10191,13 +10161,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472351</v>
+        <v>472360</v>
       </c>
       <c r="R94" t="n">
-        <v>6716551</v>
+        <v>6716688</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10254,10 +10224,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133590506</v>
+        <v>133591603</v>
       </c>
       <c r="B95" t="n">
-        <v>79116</v>
+        <v>91981</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10265,25 +10235,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -10292,13 +10270,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>472256</v>
+        <v>472351</v>
       </c>
       <c r="R95" t="n">
-        <v>6716763</v>
+        <v>6716551</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10355,10 +10333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133589818</v>
+        <v>133590632</v>
       </c>
       <c r="B96" t="n">
-        <v>57975</v>
+        <v>79116</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10366,31 +10344,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10398,10 +10371,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>472235</v>
+        <v>472275</v>
       </c>
       <c r="R96" t="n">
-        <v>6716289</v>
+        <v>6716745</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10436,17 +10409,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10465,36 +10434,44 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133590752</v>
+        <v>133591328</v>
       </c>
       <c r="B97" t="n">
-        <v>79117</v>
+        <v>93257</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -10503,13 +10480,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>472360</v>
+        <v>472372</v>
       </c>
       <c r="R97" t="n">
-        <v>6716688</v>
+        <v>6716649</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10539,6 +10516,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10566,10 +10548,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133591302</v>
+        <v>133592323</v>
       </c>
       <c r="B98" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10577,26 +10559,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10604,10 +10591,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>472353</v>
+        <v>472392</v>
       </c>
       <c r="R98" t="n">
-        <v>6716653</v>
+        <v>6716353</v>
       </c>
       <c r="S98" t="n">
         <v>50</v>
@@ -10642,13 +10629,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10667,10 +10658,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133590632</v>
+        <v>133589818</v>
       </c>
       <c r="B99" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10678,26 +10669,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10705,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472275</v>
+        <v>472235</v>
       </c>
       <c r="R99" t="n">
-        <v>6716745</v>
+        <v>6716289</v>
       </c>
       <c r="S99" t="n">
         <v>50</v>
@@ -10743,13 +10739,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10768,10 +10768,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133590480</v>
+        <v>133590506</v>
       </c>
       <c r="B100" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10779,21 +10779,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472200</v>
+        <v>472256</v>
       </c>
       <c r="R100" t="n">
-        <v>6716786</v>
+        <v>6716763</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133590286</v>
+        <v>133590480</v>
       </c>
       <c r="B101" t="n">
         <v>79359</v>
@@ -10907,13 +10907,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>472056</v>
+        <v>472200</v>
       </c>
       <c r="R101" t="n">
-        <v>6716776</v>
+        <v>6716786</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133589237</v>
+        <v>133590689</v>
       </c>
       <c r="B102" t="n">
         <v>79359</v>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472571</v>
+        <v>472273</v>
       </c>
       <c r="R102" t="n">
-        <v>6716309</v>
+        <v>6716739</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11038,12 +11038,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11071,10 +11071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133591716</v>
+        <v>133589998</v>
       </c>
       <c r="B103" t="n">
-        <v>93257</v>
+        <v>8460</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11082,48 +11082,46 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ballingstjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472427</v>
+        <v>472152</v>
       </c>
       <c r="R103" t="n">
-        <v>6716560</v>
+        <v>6716323</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11153,11 +11151,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11185,10 +11178,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133589775</v>
+        <v>133589237</v>
       </c>
       <c r="B104" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11196,21 +11189,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11223,13 +11216,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472221</v>
+        <v>472571</v>
       </c>
       <c r="R104" t="n">
-        <v>6716291</v>
+        <v>6716309</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11253,12 +11246,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11286,10 +11279,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133591678</v>
+        <v>133589694</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11297,31 +11290,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11329,10 +11317,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472376</v>
+        <v>472247</v>
       </c>
       <c r="R105" t="n">
-        <v>6716608</v>
+        <v>6716279</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11367,17 +11355,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11396,37 +11380,43 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133589694</v>
+        <v>133590595</v>
       </c>
       <c r="B106" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11434,10 +11424,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472247</v>
+        <v>472209</v>
       </c>
       <c r="R106" t="n">
-        <v>6716279</v>
+        <v>6716733</v>
       </c>
       <c r="S106" t="n">
         <v>50</v>
@@ -11497,10 +11487,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133590595</v>
+        <v>133591716</v>
       </c>
       <c r="B107" t="n">
-        <v>8460</v>
+        <v>93257</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11508,43 +11498,45 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballingstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472209</v>
+        <v>472427</v>
       </c>
       <c r="R107" t="n">
-        <v>6716733</v>
+        <v>6716560</v>
       </c>
       <c r="S107" t="n">
         <v>50</v>
@@ -11577,6 +11569,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11604,41 +11601,40 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133589998</v>
+        <v>133591678</v>
       </c>
       <c r="B108" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11648,13 +11644,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472152</v>
+        <v>472376</v>
       </c>
       <c r="R108" t="n">
-        <v>6716323</v>
+        <v>6716608</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11686,13 +11682,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11711,10 +11711,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133590689</v>
+        <v>133589775</v>
       </c>
       <c r="B109" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11722,21 +11722,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472273</v>
+        <v>472221</v>
       </c>
       <c r="R109" t="n">
-        <v>6716739</v>
+        <v>6716291</v>
       </c>
       <c r="S109" t="n">
         <v>50</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133591353</v>
+        <v>133589217</v>
       </c>
       <c r="B110" t="n">
         <v>79359</v>
@@ -11850,13 +11850,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472380</v>
+        <v>472606</v>
       </c>
       <c r="R110" t="n">
-        <v>6716634</v>
+        <v>6716343</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11913,10 +11913,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133590641</v>
+        <v>133590042</v>
       </c>
       <c r="B111" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11924,21 +11924,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11951,13 +11951,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>472258</v>
+        <v>472178</v>
       </c>
       <c r="R111" t="n">
-        <v>6716746</v>
+        <v>6716394</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12014,10 +12014,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133590042</v>
+        <v>133590679</v>
       </c>
       <c r="B112" t="n">
-        <v>79359</v>
+        <v>91981</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12025,25 +12025,33 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -12052,10 +12060,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>472178</v>
+        <v>472275</v>
       </c>
       <c r="R112" t="n">
-        <v>6716394</v>
+        <v>6716740</v>
       </c>
       <c r="S112" t="n">
         <v>50</v>
@@ -12115,7 +12123,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133590172</v>
+        <v>133589154</v>
       </c>
       <c r="B113" t="n">
         <v>79359</v>
@@ -12153,13 +12161,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>472115</v>
+        <v>472546</v>
       </c>
       <c r="R113" t="n">
-        <v>6716620</v>
+        <v>6716340</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12183,12 +12191,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12216,10 +12224,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133590679</v>
+        <v>133591353</v>
       </c>
       <c r="B114" t="n">
-        <v>91981</v>
+        <v>79359</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12227,33 +12235,25 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -12262,10 +12262,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472275</v>
+        <v>472380</v>
       </c>
       <c r="R114" t="n">
-        <v>6716740</v>
+        <v>6716634</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -12325,7 +12325,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133589217</v>
+        <v>133590172</v>
       </c>
       <c r="B115" t="n">
         <v>79359</v>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>472606</v>
+        <v>472115</v>
       </c>
       <c r="R115" t="n">
-        <v>6716343</v>
+        <v>6716620</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12426,10 +12426,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133589154</v>
+        <v>133590465</v>
       </c>
       <c r="B116" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12437,21 +12437,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>472546</v>
+        <v>472206</v>
       </c>
       <c r="R116" t="n">
-        <v>6716340</v>
+        <v>6716823</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12494,12 +12494,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12527,10 +12527,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133590465</v>
+        <v>133590641</v>
       </c>
       <c r="B117" t="n">
-        <v>79117</v>
+        <v>79116</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12538,21 +12538,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12565,13 +12565,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>472206</v>
+        <v>472258</v>
       </c>
       <c r="R117" t="n">
-        <v>6716823</v>
+        <v>6716746</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12729,37 +12729,43 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133590486</v>
+        <v>133590211</v>
       </c>
       <c r="B119" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12767,10 +12773,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>472224</v>
+        <v>472104</v>
       </c>
       <c r="R119" t="n">
-        <v>6716803</v>
+        <v>6716608</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12931,43 +12937,37 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133591564</v>
+        <v>133589883</v>
       </c>
       <c r="B121" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>472366</v>
+        <v>472271</v>
       </c>
       <c r="R121" t="n">
-        <v>6716548</v>
+        <v>6716338</v>
       </c>
       <c r="S121" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13139,43 +13139,37 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133590211</v>
+        <v>133590486</v>
       </c>
       <c r="B123" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13183,10 +13177,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>472104</v>
+        <v>472224</v>
       </c>
       <c r="R123" t="n">
-        <v>6716608</v>
+        <v>6716803</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13246,37 +13240,43 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133589883</v>
+        <v>133591564</v>
       </c>
       <c r="B124" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13284,13 +13284,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>472271</v>
+        <v>472366</v>
       </c>
       <c r="R124" t="n">
-        <v>6716338</v>
+        <v>6716548</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133591432</v>
+        <v>133589922</v>
       </c>
       <c r="B125" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13358,31 +13358,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13390,10 +13385,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472381</v>
+        <v>472188</v>
       </c>
       <c r="R125" t="n">
-        <v>6716602</v>
+        <v>6716350</v>
       </c>
       <c r="S125" t="n">
         <v>50</v>
@@ -13428,17 +13423,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13457,37 +13448,43 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133590577</v>
+        <v>133591987</v>
       </c>
       <c r="B126" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13495,10 +13492,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>472193</v>
+        <v>472419</v>
       </c>
       <c r="R126" t="n">
-        <v>6716740</v>
+        <v>6716530</v>
       </c>
       <c r="S126" t="n">
         <v>50</v>
@@ -13558,41 +13555,40 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133591987</v>
+        <v>133591432</v>
       </c>
       <c r="B127" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -13602,10 +13598,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472419</v>
+        <v>472381</v>
       </c>
       <c r="R127" t="n">
-        <v>6716530</v>
+        <v>6716602</v>
       </c>
       <c r="S127" t="n">
         <v>50</v>
@@ -13640,13 +13636,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13665,7 +13665,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133589922</v>
+        <v>133590577</v>
       </c>
       <c r="B128" t="n">
         <v>79359</v>
@@ -13703,10 +13703,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472188</v>
+        <v>472193</v>
       </c>
       <c r="R128" t="n">
-        <v>6716350</v>
+        <v>6716740</v>
       </c>
       <c r="S128" t="n">
         <v>50</v>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133590126</v>
+        <v>133592117</v>
       </c>
       <c r="B130" t="n">
         <v>79359</v>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>472123</v>
+        <v>472416</v>
       </c>
       <c r="R130" t="n">
-        <v>6716569</v>
+        <v>6716458</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133590657</v>
+        <v>133590126</v>
       </c>
       <c r="B132" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14089,31 +14089,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14121,13 +14116,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>472291</v>
+        <v>472123</v>
       </c>
       <c r="R132" t="n">
-        <v>6716730</v>
+        <v>6716569</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14159,17 +14154,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14188,7 +14179,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133592226</v>
+        <v>133589604</v>
       </c>
       <c r="B133" t="n">
         <v>79359</v>
@@ -14226,10 +14217,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472366</v>
+        <v>472376</v>
       </c>
       <c r="R133" t="n">
-        <v>6716420</v>
+        <v>6716335</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14256,12 +14247,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14289,7 +14280,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133589604</v>
+        <v>133592226</v>
       </c>
       <c r="B134" t="n">
         <v>79359</v>
@@ -14327,10 +14318,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>472376</v>
+        <v>472366</v>
       </c>
       <c r="R134" t="n">
-        <v>6716335</v>
+        <v>6716420</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14357,12 +14348,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14390,10 +14381,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133592117</v>
+        <v>133590657</v>
       </c>
       <c r="B135" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14401,26 +14392,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14428,10 +14424,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472416</v>
+        <v>472291</v>
       </c>
       <c r="R135" t="n">
-        <v>6716458</v>
+        <v>6716730</v>
       </c>
       <c r="S135" t="n">
         <v>50</v>
@@ -14466,13 +14462,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18713-2026 artfynd.xlsx
+++ b/artfynd/A 18713-2026 artfynd.xlsx
@@ -772,44 +772,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133590299</v>
+        <v>133590069</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>93264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -818,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472075</v>
+        <v>472151</v>
       </c>
       <c r="R3" t="n">
-        <v>6716793</v>
+        <v>6716422</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,6 +850,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133590549</v>
+        <v>133591484</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +920,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472261</v>
+        <v>472362</v>
       </c>
       <c r="R4" t="n">
-        <v>6716776</v>
+        <v>6716594</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133591484</v>
+        <v>133590549</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472362</v>
+        <v>472261</v>
       </c>
       <c r="R5" t="n">
-        <v>6716594</v>
+        <v>6716776</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,42 +1084,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133592266</v>
+        <v>133590299</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>91988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1126,13 +1130,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472407</v>
+        <v>472075</v>
       </c>
       <c r="R6" t="n">
-        <v>6716410</v>
+        <v>6716793</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,6 +1174,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1191,7 +1196,7 @@
         <v>133591280</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133590069</v>
+        <v>133592266</v>
       </c>
       <c r="B8" t="n">
-        <v>93257</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,30 +1305,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472151</v>
+        <v>472407</v>
       </c>
       <c r="R8" t="n">
-        <v>6716422</v>
+        <v>6716410</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1369,18 +1375,12 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från 2025</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133590302</v>
+        <v>133590160</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,26 +1410,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1437,13 +1442,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472041</v>
+        <v>472090</v>
       </c>
       <c r="R9" t="n">
-        <v>6716845</v>
+        <v>6716542</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,13 +1480,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1500,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133590494</v>
+        <v>133589761</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1520,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,13 +1547,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472235</v>
+        <v>472217</v>
       </c>
       <c r="R10" t="n">
-        <v>6716801</v>
+        <v>6716274</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133589761</v>
+        <v>133589484</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472217</v>
+        <v>472324</v>
       </c>
       <c r="R11" t="n">
-        <v>6716274</v>
+        <v>6716197</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,12 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1702,37 +1711,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133589484</v>
+        <v>133589310</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1740,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472324</v>
+        <v>472603</v>
       </c>
       <c r="R12" t="n">
-        <v>6716197</v>
+        <v>6716357</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,46 +1821,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133589310</v>
+        <v>133592241</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>8460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1850,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472603</v>
+        <v>472390</v>
       </c>
       <c r="R13" t="n">
-        <v>6716357</v>
+        <v>6716412</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1880,12 +1895,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,43 +1928,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133592241</v>
+        <v>133590302</v>
       </c>
       <c r="B14" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1957,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472390</v>
+        <v>472041</v>
       </c>
       <c r="R14" t="n">
-        <v>6716412</v>
+        <v>6716845</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2020,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133590160</v>
+        <v>133590494</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2040,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472090</v>
+        <v>472235</v>
       </c>
       <c r="R15" t="n">
-        <v>6716542</v>
+        <v>6716801</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2101,17 +2105,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133589866</v>
+        <v>133589122</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472324</v>
+        <v>472506</v>
       </c>
       <c r="R16" t="n">
-        <v>6716331</v>
+        <v>6716256</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133589122</v>
+        <v>133590542</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472506</v>
+        <v>472247</v>
       </c>
       <c r="R17" t="n">
-        <v>6716256</v>
+        <v>6716770</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133590542</v>
+        <v>133589139</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472247</v>
+        <v>472522</v>
       </c>
       <c r="R18" t="n">
-        <v>6716770</v>
+        <v>6716305</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133589139</v>
+        <v>133589866</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472522</v>
+        <v>472324</v>
       </c>
       <c r="R19" t="n">
-        <v>6716305</v>
+        <v>6716331</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133591270</v>
+        <v>133591517</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472362</v>
+        <v>472342</v>
       </c>
       <c r="R20" t="n">
-        <v>6716669</v>
+        <v>6716578</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133591517</v>
+        <v>133591270</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472342</v>
+        <v>472362</v>
       </c>
       <c r="R21" t="n">
-        <v>6716578</v>
+        <v>6716669</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2736,36 +2736,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133590308</v>
+        <v>133591800</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>93264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2774,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472127</v>
+        <v>472447</v>
       </c>
       <c r="R22" t="n">
-        <v>6716842</v>
+        <v>6716555</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2810,6 +2818,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133591252</v>
+        <v>133592104</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,10 +2888,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472357</v>
+        <v>472402</v>
       </c>
       <c r="R23" t="n">
-        <v>6716679</v>
+        <v>6716474</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2938,10 +2951,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133592104</v>
+        <v>133591252</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472402</v>
+        <v>472357</v>
       </c>
       <c r="R24" t="n">
-        <v>6716474</v>
+        <v>6716679</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3039,44 +3052,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133591800</v>
+        <v>133590308</v>
       </c>
       <c r="B25" t="n">
-        <v>93257</v>
+        <v>79123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3085,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472447</v>
+        <v>472127</v>
       </c>
       <c r="R25" t="n">
-        <v>6716555</v>
+        <v>6716842</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3121,11 +3126,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133590144</v>
+        <v>133589936</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472119</v>
+        <v>472164</v>
       </c>
       <c r="R27" t="n">
-        <v>6716583</v>
+        <v>6716349</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>133589876</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133592147</v>
+        <v>133590144</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472401</v>
+        <v>472119</v>
       </c>
       <c r="R29" t="n">
-        <v>6716444</v>
+        <v>6716583</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133589936</v>
+        <v>133592147</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472164</v>
+        <v>472401</v>
       </c>
       <c r="R30" t="n">
-        <v>6716349</v>
+        <v>6716444</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3663,7 +3663,7 @@
         <v>133589182</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133589958</v>
+        <v>133589911</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472167</v>
+        <v>472198</v>
       </c>
       <c r="R32" t="n">
-        <v>6716325</v>
+        <v>6716371</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3865,7 +3865,7 @@
         <v>133589509</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,36 +3963,44 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133590674</v>
+        <v>133590442</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>93264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4001,13 +4009,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472291</v>
+        <v>472208</v>
       </c>
       <c r="R34" t="n">
-        <v>6716730</v>
+        <v>6716811</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4037,6 +4045,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4064,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133589886</v>
+        <v>133589958</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,21 +4088,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,13 +4115,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472246</v>
+        <v>472167</v>
       </c>
       <c r="R35" t="n">
-        <v>6716353</v>
+        <v>6716325</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4165,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133590442</v>
+        <v>133590082</v>
       </c>
       <c r="B36" t="n">
-        <v>93257</v>
+        <v>8460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,34 +4189,32 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4211,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472208</v>
+        <v>472135</v>
       </c>
       <c r="R36" t="n">
-        <v>6716811</v>
+        <v>6716430</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4247,11 +4258,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4279,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133589911</v>
+        <v>133592130</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472198</v>
+        <v>472414</v>
       </c>
       <c r="R37" t="n">
-        <v>6716371</v>
+        <v>6716446</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4380,43 +4386,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133590082</v>
+        <v>133590674</v>
       </c>
       <c r="B38" t="n">
-        <v>8460</v>
+        <v>79123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472135</v>
+        <v>472291</v>
       </c>
       <c r="R38" t="n">
-        <v>6716430</v>
+        <v>6716730</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133592130</v>
+        <v>133589886</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472414</v>
+        <v>472246</v>
       </c>
       <c r="R39" t="n">
-        <v>6716446</v>
+        <v>6716353</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133591503</v>
+        <v>133592072</v>
       </c>
       <c r="B40" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472348</v>
+        <v>472386</v>
       </c>
       <c r="R40" t="n">
-        <v>6716596</v>
+        <v>6716485</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133592072</v>
+        <v>133592159</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,21 +4700,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472386</v>
+        <v>472404</v>
       </c>
       <c r="R41" t="n">
-        <v>6716485</v>
+        <v>6716455</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133592159</v>
+        <v>133589898</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4801,21 +4801,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4828,13 +4828,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472404</v>
+        <v>472233</v>
       </c>
       <c r="R42" t="n">
-        <v>6716455</v>
+        <v>6716352</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4891,43 +4891,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133590255</v>
+        <v>133591503</v>
       </c>
       <c r="B43" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4935,13 +4929,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472087</v>
+        <v>472348</v>
       </c>
       <c r="R43" t="n">
-        <v>6716742</v>
+        <v>6716596</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4998,37 +4992,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133589898</v>
+        <v>133590255</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472233</v>
+        <v>472087</v>
       </c>
       <c r="R44" t="n">
-        <v>6716352</v>
+        <v>6716742</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133590561</v>
+        <v>133589715</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472249</v>
+        <v>472246</v>
       </c>
       <c r="R45" t="n">
-        <v>6716778</v>
+        <v>6716249</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133590454</v>
+        <v>133590561</v>
       </c>
       <c r="B46" t="n">
-        <v>79117</v>
+        <v>79123</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,13 +5238,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472220</v>
+        <v>472249</v>
       </c>
       <c r="R46" t="n">
-        <v>6716814</v>
+        <v>6716778</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133589839</v>
+        <v>133589832</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5312,26 +5312,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5339,13 +5344,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472288</v>
+        <v>472206</v>
       </c>
       <c r="R47" t="n">
-        <v>6716309</v>
+        <v>6716317</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5377,13 +5382,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5402,10 +5411,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133590570</v>
+        <v>133590454</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5413,21 +5422,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5440,13 +5449,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472257</v>
+        <v>472220</v>
       </c>
       <c r="R48" t="n">
-        <v>6716771</v>
+        <v>6716814</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5506,7 +5515,7 @@
         <v>133589949</v>
       </c>
       <c r="B49" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5604,10 +5613,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133589715</v>
+        <v>133589839</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,13 +5651,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472246</v>
+        <v>472288</v>
       </c>
       <c r="R50" t="n">
-        <v>6716249</v>
+        <v>6716309</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5705,10 +5714,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133589832</v>
+        <v>133590570</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>79123</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,31 +5725,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5748,10 +5752,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472206</v>
+        <v>472257</v>
       </c>
       <c r="R51" t="n">
-        <v>6716317</v>
+        <v>6716771</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5786,17 +5790,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5815,48 +5815,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133590280</v>
+        <v>133591871</v>
       </c>
       <c r="B52" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ballthjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>472057</v>
+        <v>472421</v>
       </c>
       <c r="R52" t="n">
-        <v>6716745</v>
+        <v>6716519</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5897,7 +5902,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5916,10 +5920,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133589660</v>
+        <v>133589557</v>
       </c>
       <c r="B53" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5954,13 +5958,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>472264</v>
+        <v>472355</v>
       </c>
       <c r="R53" t="n">
-        <v>6716238</v>
+        <v>6716306</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5984,12 +5988,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6017,10 +6021,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133589789</v>
+        <v>133590280</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,14 +6055,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballthjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>472223</v>
+        <v>472057</v>
       </c>
       <c r="R54" t="n">
-        <v>6716268</v>
+        <v>6716745</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6118,10 +6122,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133592299</v>
+        <v>133589789</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,10 +6160,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>472393</v>
+        <v>472223</v>
       </c>
       <c r="R55" t="n">
-        <v>6716395</v>
+        <v>6716268</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6219,42 +6223,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133591871</v>
+        <v>133589660</v>
       </c>
       <c r="B56" t="n">
-        <v>57162</v>
+        <v>79366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6262,10 +6261,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>472421</v>
+        <v>472264</v>
       </c>
       <c r="R56" t="n">
-        <v>6716519</v>
+        <v>6716238</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6306,6 +6305,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>133590101</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6425,42 +6425,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133591759</v>
+        <v>133592299</v>
       </c>
       <c r="B58" t="n">
-        <v>57162</v>
+        <v>79366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>472442</v>
+        <v>472393</v>
       </c>
       <c r="R58" t="n">
-        <v>6716568</v>
+        <v>6716395</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6512,6 +6507,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6530,37 +6526,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133589557</v>
+        <v>133591759</v>
       </c>
       <c r="B59" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6568,13 +6569,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>472355</v>
+        <v>472442</v>
       </c>
       <c r="R59" t="n">
-        <v>6716306</v>
+        <v>6716568</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6598,12 +6599,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6612,7 +6613,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>133589587</v>
       </c>
       <c r="B60" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6732,10 +6732,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133590189</v>
+        <v>133589426</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6770,13 +6770,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>472100</v>
+        <v>472436</v>
       </c>
       <c r="R61" t="n">
-        <v>6716639</v>
+        <v>6716208</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,10 +6833,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133590240</v>
+        <v>133590189</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6844,21 +6844,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>472083</v>
+        <v>472100</v>
       </c>
       <c r="R62" t="n">
-        <v>6716723</v>
+        <v>6716639</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6934,37 +6934,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133590417</v>
+        <v>133592346</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>57162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>472173</v>
+        <v>472396</v>
       </c>
       <c r="R63" t="n">
-        <v>6716842</v>
+        <v>6716339</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7010,13 +7015,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Betad tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7035,10 +7044,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133590624</v>
+        <v>133590240</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7073,13 +7082,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>472263</v>
+        <v>472083</v>
       </c>
       <c r="R64" t="n">
-        <v>6716734</v>
+        <v>6716723</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7136,10 +7145,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133590405</v>
+        <v>133591819</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7174,10 +7183,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472190</v>
+        <v>472431</v>
       </c>
       <c r="R65" t="n">
-        <v>6716830</v>
+        <v>6716531</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7237,10 +7246,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133590028</v>
+        <v>133589444</v>
       </c>
       <c r="B66" t="n">
-        <v>79117</v>
+        <v>79123</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,21 +7257,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7275,10 +7284,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472152</v>
+        <v>472312</v>
       </c>
       <c r="R66" t="n">
-        <v>6716346</v>
+        <v>6716221</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7305,12 +7314,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7338,10 +7347,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133590319</v>
+        <v>133590417</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7349,21 +7358,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7385,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472145</v>
+        <v>472173</v>
       </c>
       <c r="R67" t="n">
-        <v>6716826</v>
+        <v>6716842</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7439,10 +7448,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133589201</v>
+        <v>133589629</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7450,21 +7459,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7477,10 +7486,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472581</v>
+        <v>472318</v>
       </c>
       <c r="R68" t="n">
-        <v>6716345</v>
+        <v>6716281</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7540,10 +7549,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133591819</v>
+        <v>133589542</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7551,26 +7560,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7578,13 +7592,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472431</v>
+        <v>472359</v>
       </c>
       <c r="R69" t="n">
-        <v>6716531</v>
+        <v>6716287</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7608,12 +7622,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7622,7 +7641,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7641,10 +7659,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133589426</v>
+        <v>133590624</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,21 +7670,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7679,13 +7697,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472436</v>
+        <v>472263</v>
       </c>
       <c r="R70" t="n">
-        <v>6716208</v>
+        <v>6716734</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7709,12 +7727,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7742,10 +7760,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133589444</v>
+        <v>133590028</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7753,21 +7771,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7780,10 +7798,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472312</v>
+        <v>472152</v>
       </c>
       <c r="R71" t="n">
-        <v>6716221</v>
+        <v>6716346</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7810,12 +7828,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7843,10 +7861,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133589629</v>
+        <v>133589201</v>
       </c>
       <c r="B72" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7854,21 +7872,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7881,10 +7899,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472318</v>
+        <v>472581</v>
       </c>
       <c r="R72" t="n">
-        <v>6716281</v>
+        <v>6716345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7944,42 +7962,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133592346</v>
+        <v>133590405</v>
       </c>
       <c r="B73" t="n">
-        <v>57162</v>
+        <v>79123</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7987,10 +8000,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472396</v>
+        <v>472190</v>
       </c>
       <c r="R73" t="n">
-        <v>6716339</v>
+        <v>6716830</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8025,17 +8038,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Betad tall.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8054,10 +8063,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133589542</v>
+        <v>133590319</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8065,31 +8074,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8097,13 +8101,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472359</v>
+        <v>472145</v>
       </c>
       <c r="R74" t="n">
-        <v>6716287</v>
+        <v>6716826</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8127,17 +8131,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8146,6 +8145,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8164,10 +8164,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133590498</v>
+        <v>133590202</v>
       </c>
       <c r="B75" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472251</v>
+        <v>472083</v>
       </c>
       <c r="R75" t="n">
-        <v>6716795</v>
+        <v>6716615</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8265,37 +8265,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133590038</v>
+        <v>133590013</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>57162</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472157</v>
+        <v>472122</v>
       </c>
       <c r="R76" t="n">
-        <v>6716343</v>
+        <v>6716329</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8341,13 +8346,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8366,10 +8375,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133589670</v>
+        <v>133590498</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8404,10 +8413,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472280</v>
+        <v>472251</v>
       </c>
       <c r="R77" t="n">
-        <v>6716266</v>
+        <v>6716795</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8467,10 +8476,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133590202</v>
+        <v>133589670</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8505,10 +8514,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472083</v>
+        <v>472280</v>
       </c>
       <c r="R78" t="n">
-        <v>6716615</v>
+        <v>6716266</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -8568,42 +8577,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133590013</v>
+        <v>133590038</v>
       </c>
       <c r="B79" t="n">
-        <v>57162</v>
+        <v>79123</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8611,10 +8615,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>472122</v>
+        <v>472157</v>
       </c>
       <c r="R79" t="n">
-        <v>6716329</v>
+        <v>6716343</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8649,17 +8653,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Betad tall</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>133589849</v>
       </c>
       <c r="B80" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133590053</v>
+        <v>133590135</v>
       </c>
       <c r="B81" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472187</v>
+        <v>472107</v>
       </c>
       <c r="R81" t="n">
-        <v>6716406</v>
+        <v>6716575</v>
       </c>
       <c r="S81" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133591463</v>
+        <v>133590391</v>
       </c>
       <c r="B82" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8891,26 +8891,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8918,10 +8923,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>472372</v>
+        <v>472175</v>
       </c>
       <c r="R82" t="n">
-        <v>6716600</v>
+        <v>6716830</v>
       </c>
       <c r="S82" t="n">
         <v>50</v>
@@ -8956,13 +8961,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8981,10 +8990,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133589470</v>
+        <v>133591463</v>
       </c>
       <c r="B83" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9019,13 +9028,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>472321</v>
+        <v>472372</v>
       </c>
       <c r="R83" t="n">
-        <v>6716236</v>
+        <v>6716600</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9049,12 +9058,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9082,10 +9091,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133589858</v>
+        <v>133591528</v>
       </c>
       <c r="B84" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9120,13 +9129,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>472330</v>
+        <v>472337</v>
       </c>
       <c r="R84" t="n">
-        <v>6716313</v>
+        <v>6716585</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9183,10 +9192,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133590229</v>
+        <v>133590113</v>
       </c>
       <c r="B85" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9221,10 +9230,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>472048</v>
+        <v>472116</v>
       </c>
       <c r="R85" t="n">
-        <v>6716642</v>
+        <v>6716545</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -9284,10 +9293,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133590113</v>
+        <v>133589470</v>
       </c>
       <c r="B86" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9322,13 +9331,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>472116</v>
+        <v>472321</v>
       </c>
       <c r="R86" t="n">
-        <v>6716545</v>
+        <v>6716236</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9352,12 +9361,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9385,10 +9394,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133590135</v>
+        <v>133589858</v>
       </c>
       <c r="B87" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9423,10 +9432,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>472107</v>
+        <v>472330</v>
       </c>
       <c r="R87" t="n">
-        <v>6716575</v>
+        <v>6716313</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9486,10 +9495,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133591528</v>
+        <v>133590053</v>
       </c>
       <c r="B88" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9524,10 +9533,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>472337</v>
+        <v>472187</v>
       </c>
       <c r="R88" t="n">
-        <v>6716585</v>
+        <v>6716406</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -9697,44 +9706,36 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133592016</v>
+        <v>133590229</v>
       </c>
       <c r="B90" t="n">
-        <v>93257</v>
+        <v>79366</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -9743,10 +9744,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>472439</v>
+        <v>472048</v>
       </c>
       <c r="R90" t="n">
-        <v>6716486</v>
+        <v>6716642</v>
       </c>
       <c r="S90" t="n">
         <v>50</v>
@@ -9779,11 +9780,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9811,42 +9807,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133590391</v>
+        <v>133592016</v>
       </c>
       <c r="B91" t="n">
-        <v>57975</v>
+        <v>93264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -9854,10 +9853,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472175</v>
+        <v>472439</v>
       </c>
       <c r="R91" t="n">
-        <v>6716830</v>
+        <v>6716486</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -9894,7 +9893,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9903,6 +9902,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9921,36 +9921,44 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133590286</v>
+        <v>133591328</v>
       </c>
       <c r="B92" t="n">
-        <v>79359</v>
+        <v>93264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -9959,10 +9967,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>472056</v>
+        <v>472372</v>
       </c>
       <c r="R92" t="n">
-        <v>6716776</v>
+        <v>6716649</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -9995,6 +10003,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10022,10 +10035,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133591302</v>
+        <v>133592323</v>
       </c>
       <c r="B93" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10033,26 +10046,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10060,10 +10078,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472353</v>
+        <v>472392</v>
       </c>
       <c r="R93" t="n">
-        <v>6716653</v>
+        <v>6716353</v>
       </c>
       <c r="S93" t="n">
         <v>50</v>
@@ -10098,13 +10116,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10123,10 +10145,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133590752</v>
+        <v>133591603</v>
       </c>
       <c r="B94" t="n">
-        <v>79117</v>
+        <v>91988</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10134,25 +10156,33 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -10161,13 +10191,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472360</v>
+        <v>472351</v>
       </c>
       <c r="R94" t="n">
-        <v>6716688</v>
+        <v>6716551</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10224,10 +10254,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133591603</v>
+        <v>133590506</v>
       </c>
       <c r="B95" t="n">
-        <v>91981</v>
+        <v>79123</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10235,33 +10265,25 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -10270,13 +10292,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>472351</v>
+        <v>472256</v>
       </c>
       <c r="R95" t="n">
-        <v>6716551</v>
+        <v>6716763</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10333,10 +10355,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133590632</v>
+        <v>133589818</v>
       </c>
       <c r="B96" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10344,26 +10366,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10371,10 +10398,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>472275</v>
+        <v>472235</v>
       </c>
       <c r="R96" t="n">
-        <v>6716745</v>
+        <v>6716289</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10409,13 +10436,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10434,44 +10465,36 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133591328</v>
+        <v>133590752</v>
       </c>
       <c r="B97" t="n">
-        <v>93257</v>
+        <v>79124</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -10480,13 +10503,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>472372</v>
+        <v>472360</v>
       </c>
       <c r="R97" t="n">
-        <v>6716649</v>
+        <v>6716688</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10516,11 +10539,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10548,10 +10566,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133592323</v>
+        <v>133591302</v>
       </c>
       <c r="B98" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10559,31 +10577,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10591,10 +10604,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>472392</v>
+        <v>472353</v>
       </c>
       <c r="R98" t="n">
-        <v>6716353</v>
+        <v>6716653</v>
       </c>
       <c r="S98" t="n">
         <v>50</v>
@@ -10629,17 +10642,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10658,10 +10667,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133589818</v>
+        <v>133590632</v>
       </c>
       <c r="B99" t="n">
-        <v>57975</v>
+        <v>79123</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10669,31 +10678,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10701,10 +10705,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>472235</v>
+        <v>472275</v>
       </c>
       <c r="R99" t="n">
-        <v>6716289</v>
+        <v>6716745</v>
       </c>
       <c r="S99" t="n">
         <v>50</v>
@@ -10739,17 +10743,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10768,10 +10768,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133590506</v>
+        <v>133590480</v>
       </c>
       <c r="B100" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10779,21 +10779,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472256</v>
+        <v>472200</v>
       </c>
       <c r="R100" t="n">
-        <v>6716763</v>
+        <v>6716786</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10869,10 +10869,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133590480</v>
+        <v>133590286</v>
       </c>
       <c r="B101" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10907,13 +10907,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>472200</v>
+        <v>472056</v>
       </c>
       <c r="R101" t="n">
-        <v>6716786</v>
+        <v>6716776</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10970,10 +10970,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133590689</v>
+        <v>133589237</v>
       </c>
       <c r="B102" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472273</v>
+        <v>472571</v>
       </c>
       <c r="R102" t="n">
-        <v>6716739</v>
+        <v>6716309</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11038,12 +11038,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11071,43 +11071,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133589998</v>
+        <v>133589775</v>
       </c>
       <c r="B103" t="n">
-        <v>8460</v>
+        <v>79123</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11115,13 +11109,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472152</v>
+        <v>472221</v>
       </c>
       <c r="R103" t="n">
-        <v>6716323</v>
+        <v>6716291</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11178,51 +11172,59 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133589237</v>
+        <v>133591716</v>
       </c>
       <c r="B104" t="n">
-        <v>79359</v>
+        <v>93264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballingstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472571</v>
+        <v>472427</v>
       </c>
       <c r="R104" t="n">
-        <v>6716309</v>
+        <v>6716560</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11246,12 +11248,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11279,10 +11286,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133589694</v>
+        <v>133591678</v>
       </c>
       <c r="B105" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11290,26 +11297,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11317,10 +11329,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472247</v>
+        <v>472376</v>
       </c>
       <c r="R105" t="n">
-        <v>6716279</v>
+        <v>6716608</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11355,13 +11367,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11380,43 +11396,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133590595</v>
+        <v>133589694</v>
       </c>
       <c r="B106" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11424,10 +11434,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472209</v>
+        <v>472247</v>
       </c>
       <c r="R106" t="n">
-        <v>6716733</v>
+        <v>6716279</v>
       </c>
       <c r="S106" t="n">
         <v>50</v>
@@ -11487,10 +11497,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133591716</v>
+        <v>133590595</v>
       </c>
       <c r="B107" t="n">
-        <v>93257</v>
+        <v>8460</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11498,45 +11508,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ballingstjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472427</v>
+        <v>472209</v>
       </c>
       <c r="R107" t="n">
-        <v>6716560</v>
+        <v>6716733</v>
       </c>
       <c r="S107" t="n">
         <v>50</v>
@@ -11569,11 +11577,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11601,40 +11604,41 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133591678</v>
+        <v>133589998</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>8460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11644,13 +11648,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472376</v>
+        <v>472152</v>
       </c>
       <c r="R108" t="n">
-        <v>6716608</v>
+        <v>6716323</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11682,17 +11686,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11711,10 +11711,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133589775</v>
+        <v>133590689</v>
       </c>
       <c r="B109" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11722,21 +11722,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472221</v>
+        <v>472273</v>
       </c>
       <c r="R109" t="n">
-        <v>6716291</v>
+        <v>6716739</v>
       </c>
       <c r="S109" t="n">
         <v>50</v>
@@ -11812,10 +11812,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133589217</v>
+        <v>133590641</v>
       </c>
       <c r="B110" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11823,21 +11823,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472606</v>
+        <v>472258</v>
       </c>
       <c r="R110" t="n">
-        <v>6716343</v>
+        <v>6716746</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11913,10 +11913,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133590042</v>
+        <v>133590172</v>
       </c>
       <c r="B111" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,10 +11951,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>472178</v>
+        <v>472115</v>
       </c>
       <c r="R111" t="n">
-        <v>6716394</v>
+        <v>6716620</v>
       </c>
       <c r="S111" t="n">
         <v>50</v>
@@ -12014,10 +12014,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133590679</v>
+        <v>133591353</v>
       </c>
       <c r="B112" t="n">
-        <v>91981</v>
+        <v>79366</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12025,33 +12025,25 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -12060,10 +12052,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>472275</v>
+        <v>472380</v>
       </c>
       <c r="R112" t="n">
-        <v>6716740</v>
+        <v>6716634</v>
       </c>
       <c r="S112" t="n">
         <v>50</v>
@@ -12123,10 +12115,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133589154</v>
+        <v>133590042</v>
       </c>
       <c r="B113" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12161,13 +12153,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>472546</v>
+        <v>472178</v>
       </c>
       <c r="R113" t="n">
-        <v>6716340</v>
+        <v>6716394</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12191,12 +12183,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12224,10 +12216,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133591353</v>
+        <v>133589154</v>
       </c>
       <c r="B114" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12262,13 +12254,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472380</v>
+        <v>472546</v>
       </c>
       <c r="R114" t="n">
-        <v>6716634</v>
+        <v>6716340</v>
       </c>
       <c r="S114" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12292,12 +12284,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12325,10 +12317,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133590172</v>
+        <v>133590679</v>
       </c>
       <c r="B115" t="n">
-        <v>79359</v>
+        <v>91988</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12336,25 +12328,33 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>472115</v>
+        <v>472275</v>
       </c>
       <c r="R115" t="n">
-        <v>6716620</v>
+        <v>6716740</v>
       </c>
       <c r="S115" t="n">
         <v>50</v>
@@ -12426,10 +12426,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133590465</v>
+        <v>133589217</v>
       </c>
       <c r="B116" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12437,21 +12437,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>472206</v>
+        <v>472606</v>
       </c>
       <c r="R116" t="n">
-        <v>6716823</v>
+        <v>6716343</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12494,12 +12494,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12527,10 +12527,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133590641</v>
+        <v>133590465</v>
       </c>
       <c r="B117" t="n">
-        <v>79116</v>
+        <v>79124</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12538,21 +12538,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12565,13 +12565,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>472258</v>
+        <v>472206</v>
       </c>
       <c r="R117" t="n">
-        <v>6716746</v>
+        <v>6716823</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>133592036</v>
       </c>
       <c r="B118" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12729,43 +12729,37 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133590211</v>
+        <v>133590486</v>
       </c>
       <c r="B119" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12773,10 +12767,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>472104</v>
+        <v>472224</v>
       </c>
       <c r="R119" t="n">
-        <v>6716608</v>
+        <v>6716803</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12839,7 +12833,7 @@
         <v>133591547</v>
       </c>
       <c r="B120" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12937,37 +12931,43 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133589883</v>
+        <v>133591564</v>
       </c>
       <c r="B121" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>472271</v>
+        <v>472366</v>
       </c>
       <c r="R121" t="n">
-        <v>6716338</v>
+        <v>6716548</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13038,37 +13038,43 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133590047</v>
+        <v>133590211</v>
       </c>
       <c r="B122" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13076,13 +13082,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>472171</v>
+        <v>472104</v>
       </c>
       <c r="R122" t="n">
-        <v>6716408</v>
+        <v>6716608</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13139,10 +13145,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133590486</v>
+        <v>133589883</v>
       </c>
       <c r="B123" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13177,10 +13183,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>472224</v>
+        <v>472271</v>
       </c>
       <c r="R123" t="n">
-        <v>6716803</v>
+        <v>6716338</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13240,43 +13246,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133591564</v>
+        <v>133590047</v>
       </c>
       <c r="B124" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>472366</v>
+        <v>472171</v>
       </c>
       <c r="R124" t="n">
-        <v>6716548</v>
+        <v>6716408</v>
       </c>
       <c r="S124" t="n">
         <v>50</v>
@@ -13347,10 +13347,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133589922</v>
+        <v>133591432</v>
       </c>
       <c r="B125" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13358,26 +13358,31 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -13385,10 +13390,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472188</v>
+        <v>472381</v>
       </c>
       <c r="R125" t="n">
-        <v>6716350</v>
+        <v>6716602</v>
       </c>
       <c r="S125" t="n">
         <v>50</v>
@@ -13423,13 +13428,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13448,43 +13457,37 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133591987</v>
+        <v>133590577</v>
       </c>
       <c r="B126" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13492,10 +13495,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>472419</v>
+        <v>472193</v>
       </c>
       <c r="R126" t="n">
-        <v>6716530</v>
+        <v>6716740</v>
       </c>
       <c r="S126" t="n">
         <v>50</v>
@@ -13555,40 +13558,41 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133591432</v>
+        <v>133591987</v>
       </c>
       <c r="B127" t="n">
-        <v>57975</v>
+        <v>8460</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -13598,10 +13602,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472381</v>
+        <v>472419</v>
       </c>
       <c r="R127" t="n">
-        <v>6716602</v>
+        <v>6716530</v>
       </c>
       <c r="S127" t="n">
         <v>50</v>
@@ -13636,17 +13640,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13665,10 +13665,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133590577</v>
+        <v>133589922</v>
       </c>
       <c r="B128" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13703,10 +13703,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472193</v>
+        <v>472188</v>
       </c>
       <c r="R128" t="n">
-        <v>6716740</v>
+        <v>6716350</v>
       </c>
       <c r="S128" t="n">
         <v>50</v>
@@ -13769,7 +13769,7 @@
         <v>133589343</v>
       </c>
       <c r="B129" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13876,10 +13876,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133592117</v>
+        <v>133590126</v>
       </c>
       <c r="B130" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>472416</v>
+        <v>472123</v>
       </c>
       <c r="R130" t="n">
-        <v>6716458</v>
+        <v>6716569</v>
       </c>
       <c r="S130" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>133592281</v>
       </c>
       <c r="B131" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14078,10 +14078,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133590126</v>
+        <v>133590657</v>
       </c>
       <c r="B132" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14089,26 +14089,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14116,13 +14121,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>472123</v>
+        <v>472291</v>
       </c>
       <c r="R132" t="n">
-        <v>6716569</v>
+        <v>6716730</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14154,13 +14159,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14179,10 +14188,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133589604</v>
+        <v>133592226</v>
       </c>
       <c r="B133" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14217,10 +14226,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472376</v>
+        <v>472366</v>
       </c>
       <c r="R133" t="n">
-        <v>6716335</v>
+        <v>6716420</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14247,12 +14256,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14280,10 +14289,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133592226</v>
+        <v>133589604</v>
       </c>
       <c r="B134" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14318,10 +14327,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>472366</v>
+        <v>472376</v>
       </c>
       <c r="R134" t="n">
-        <v>6716420</v>
+        <v>6716335</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14348,12 +14357,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14381,10 +14390,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133590657</v>
+        <v>133592117</v>
       </c>
       <c r="B135" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14392,31 +14401,26 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14424,10 +14428,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472291</v>
+        <v>472416</v>
       </c>
       <c r="R135" t="n">
-        <v>6716730</v>
+        <v>6716458</v>
       </c>
       <c r="S135" t="n">
         <v>50</v>
@@ -14462,17 +14466,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18713-2026 artfynd.xlsx
+++ b/artfynd/A 18713-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129828593</v>
+        <v>133589402</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ballstjärnen, Ballstjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472089</v>
+        <v>472449</v>
       </c>
       <c r="R2" t="n">
-        <v>6716793</v>
+        <v>6716212</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från höst 2025.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,18 +766,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,11 +788,11 @@
         <v>133590069</v>
       </c>
       <c r="B3" t="n">
-        <v>93264</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133591484</v>
+        <v>133590442</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,25 +906,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -920,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472362</v>
+        <v>472208</v>
       </c>
       <c r="R4" t="n">
-        <v>6716594</v>
+        <v>6716811</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -956,6 +977,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133590549</v>
+        <v>133591328</v>
       </c>
       <c r="B5" t="n">
-        <v>79123</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,25 +1020,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472261</v>
+        <v>472372</v>
       </c>
       <c r="R5" t="n">
-        <v>6716776</v>
+        <v>6716649</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1057,6 +1091,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133590299</v>
+        <v>133591716</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>93271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,26 +1134,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1126,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballingstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472075</v>
+        <v>472427</v>
       </c>
       <c r="R6" t="n">
-        <v>6716793</v>
+        <v>6716560</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1166,6 +1205,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133591280</v>
+        <v>133591800</v>
       </c>
       <c r="B7" t="n">
-        <v>79123</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,25 +1248,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1231,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472347</v>
+        <v>472447</v>
       </c>
       <c r="R7" t="n">
-        <v>6716671</v>
+        <v>6716555</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1267,6 +1319,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,42 +1351,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133592266</v>
+        <v>133592016</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1337,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472407</v>
+        <v>472439</v>
       </c>
       <c r="R8" t="n">
-        <v>6716410</v>
+        <v>6716486</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,12 +1435,18 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Från 2025</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133590160</v>
+        <v>133590299</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>91995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,31 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1442,13 +1511,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472090</v>
+        <v>472075</v>
       </c>
       <c r="R9" t="n">
-        <v>6716542</v>
+        <v>6716793</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1480,17 +1549,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1509,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133589761</v>
+        <v>133590679</v>
       </c>
       <c r="B10" t="n">
-        <v>79123</v>
+        <v>91995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,25 +1585,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1547,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472217</v>
+        <v>472275</v>
       </c>
       <c r="R10" t="n">
-        <v>6716274</v>
+        <v>6716740</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1610,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133589484</v>
+        <v>133591603</v>
       </c>
       <c r="B11" t="n">
-        <v>79123</v>
+        <v>91995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,25 +1694,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1648,13 +1729,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472324</v>
+        <v>472351</v>
       </c>
       <c r="R11" t="n">
-        <v>6716197</v>
+        <v>6716551</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,12 +1759,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133589310</v>
+        <v>129828593</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1722,49 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballstjärnen, Ballstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472603</v>
+        <v>472089</v>
       </c>
       <c r="R12" t="n">
-        <v>6716357</v>
+        <v>6716793</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,12 +1857,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,62 +1871,55 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133592241</v>
+        <v>133589122</v>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1865,13 +1927,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472390</v>
+        <v>472506</v>
       </c>
       <c r="R13" t="n">
-        <v>6716412</v>
+        <v>6716256</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1895,12 +1957,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,14 +1990,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133590302</v>
+        <v>133589139</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1966,13 +2028,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472041</v>
+        <v>472522</v>
       </c>
       <c r="R14" t="n">
-        <v>6716845</v>
+        <v>6716305</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1996,12 +2058,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,14 +2091,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133590494</v>
+        <v>133589154</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2067,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472235</v>
+        <v>472546</v>
       </c>
       <c r="R15" t="n">
-        <v>6716801</v>
+        <v>6716340</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2097,12 +2159,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,14 +2192,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133589122</v>
+        <v>133589182</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2168,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472506</v>
+        <v>472576</v>
       </c>
       <c r="R16" t="n">
-        <v>6716256</v>
+        <v>6716372</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2231,32 +2293,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133590542</v>
+        <v>133589201</v>
       </c>
       <c r="B17" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472247</v>
+        <v>472581</v>
       </c>
       <c r="R17" t="n">
-        <v>6716770</v>
+        <v>6716345</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2299,12 +2361,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,14 +2394,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133589139</v>
+        <v>133589217</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2370,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472522</v>
+        <v>472606</v>
       </c>
       <c r="R18" t="n">
-        <v>6716305</v>
+        <v>6716343</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2433,14 +2495,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133589866</v>
+        <v>133589237</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2471,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472324</v>
+        <v>472571</v>
       </c>
       <c r="R19" t="n">
-        <v>6716331</v>
+        <v>6716309</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2501,12 +2563,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,14 +2596,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133591517</v>
+        <v>133589426</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2572,13 +2634,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472342</v>
+        <v>472436</v>
       </c>
       <c r="R20" t="n">
-        <v>6716578</v>
+        <v>6716208</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2602,12 +2664,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,32 +2697,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133591270</v>
+        <v>133589470</v>
       </c>
       <c r="B21" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,13 +2735,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472362</v>
+        <v>472321</v>
       </c>
       <c r="R21" t="n">
-        <v>6716669</v>
+        <v>6716236</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2703,12 +2765,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,44 +2798,36 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133591800</v>
+        <v>133589509</v>
       </c>
       <c r="B22" t="n">
-        <v>93264</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2782,13 +2836,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472447</v>
+        <v>472356</v>
       </c>
       <c r="R22" t="n">
-        <v>6716555</v>
+        <v>6716261</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2812,17 +2866,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,14 +2899,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133592104</v>
+        <v>133589557</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2888,13 +2937,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472402</v>
+        <v>472355</v>
       </c>
       <c r="R23" t="n">
-        <v>6716474</v>
+        <v>6716306</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2918,12 +2967,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,14 +3000,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133591252</v>
+        <v>133589587</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2989,13 +3038,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472357</v>
+        <v>472365</v>
       </c>
       <c r="R24" t="n">
-        <v>6716679</v>
+        <v>6716324</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,12 +3068,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,32 +3101,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133590308</v>
+        <v>133589604</v>
       </c>
       <c r="B25" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,13 +3139,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472127</v>
+        <v>472376</v>
       </c>
       <c r="R25" t="n">
-        <v>6716842</v>
+        <v>6716335</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,12 +3169,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,39 +3202,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133591313</v>
+        <v>133589660</v>
       </c>
       <c r="B26" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3193,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472361</v>
+        <v>472264</v>
       </c>
       <c r="R26" t="n">
-        <v>6716656</v>
+        <v>6716238</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3256,14 +3303,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133589936</v>
+        <v>133589670</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3294,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472164</v>
+        <v>472280</v>
       </c>
       <c r="R27" t="n">
-        <v>6716349</v>
+        <v>6716266</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3357,14 +3404,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133589876</v>
+        <v>133589694</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3395,13 +3442,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472294</v>
+        <v>472247</v>
       </c>
       <c r="R28" t="n">
-        <v>6716338</v>
+        <v>6716279</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3458,14 +3505,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133590144</v>
+        <v>133589715</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3496,13 +3543,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472119</v>
+        <v>472246</v>
       </c>
       <c r="R29" t="n">
-        <v>6716583</v>
+        <v>6716249</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,14 +3606,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133592147</v>
+        <v>133589789</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3597,10 +3644,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472401</v>
+        <v>472223</v>
       </c>
       <c r="R30" t="n">
-        <v>6716444</v>
+        <v>6716268</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3660,14 +3707,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133589182</v>
+        <v>133589839</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3698,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472576</v>
+        <v>472288</v>
       </c>
       <c r="R31" t="n">
-        <v>6716372</v>
+        <v>6716309</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3728,12 +3775,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3761,14 +3808,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133589911</v>
+        <v>133589849</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3799,13 +3846,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472198</v>
+        <v>472309</v>
       </c>
       <c r="R32" t="n">
-        <v>6716371</v>
+        <v>6716305</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3862,14 +3909,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133589509</v>
+        <v>133589858</v>
       </c>
       <c r="B33" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3900,10 +3947,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472356</v>
+        <v>472330</v>
       </c>
       <c r="R33" t="n">
-        <v>6716261</v>
+        <v>6716313</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3930,12 +3977,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,44 +4010,36 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133590442</v>
+        <v>133589866</v>
       </c>
       <c r="B34" t="n">
-        <v>93264</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4009,10 +4048,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472208</v>
+        <v>472324</v>
       </c>
       <c r="R34" t="n">
-        <v>6716811</v>
+        <v>6716331</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4045,11 +4084,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Från hösten 2025.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4077,32 +4111,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133589958</v>
+        <v>133589876</v>
       </c>
       <c r="B35" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4115,13 +4149,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472167</v>
+        <v>472294</v>
       </c>
       <c r="R35" t="n">
-        <v>6716325</v>
+        <v>6716338</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,43 +4212,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133590082</v>
+        <v>133589883</v>
       </c>
       <c r="B36" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4222,10 +4250,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472135</v>
+        <v>472271</v>
       </c>
       <c r="R36" t="n">
-        <v>6716430</v>
+        <v>6716338</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4285,14 +4313,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133592130</v>
+        <v>133589886</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4323,13 +4351,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472414</v>
+        <v>472246</v>
       </c>
       <c r="R37" t="n">
-        <v>6716446</v>
+        <v>6716353</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4386,32 +4414,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133590674</v>
+        <v>133589898</v>
       </c>
       <c r="B38" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4424,13 +4452,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472291</v>
+        <v>472233</v>
       </c>
       <c r="R38" t="n">
-        <v>6716730</v>
+        <v>6716352</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4487,14 +4515,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133589886</v>
+        <v>133589911</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4525,13 +4553,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472246</v>
+        <v>472198</v>
       </c>
       <c r="R39" t="n">
-        <v>6716353</v>
+        <v>6716371</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4588,14 +4616,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133592072</v>
+        <v>133589922</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4626,10 +4654,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472386</v>
+        <v>472188</v>
       </c>
       <c r="R40" t="n">
-        <v>6716485</v>
+        <v>6716350</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4689,32 +4717,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133592159</v>
+        <v>133589936</v>
       </c>
       <c r="B41" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4727,10 +4755,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472404</v>
+        <v>472164</v>
       </c>
       <c r="R41" t="n">
-        <v>6716455</v>
+        <v>6716349</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4790,14 +4818,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133589898</v>
+        <v>133589949</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4828,13 +4856,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472233</v>
+        <v>472174</v>
       </c>
       <c r="R42" t="n">
-        <v>6716352</v>
+        <v>6716377</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4891,14 +4919,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133591503</v>
+        <v>133590042</v>
       </c>
       <c r="B43" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4929,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472348</v>
+        <v>472178</v>
       </c>
       <c r="R43" t="n">
-        <v>6716596</v>
+        <v>6716394</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4992,43 +5020,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133590255</v>
+        <v>133590047</v>
       </c>
       <c r="B44" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5036,13 +5058,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472087</v>
+        <v>472171</v>
       </c>
       <c r="R44" t="n">
-        <v>6716742</v>
+        <v>6716408</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5099,14 +5121,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133589715</v>
+        <v>133590053</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5137,10 +5159,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472246</v>
+        <v>472187</v>
       </c>
       <c r="R45" t="n">
-        <v>6716249</v>
+        <v>6716406</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5200,32 +5222,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133590561</v>
+        <v>133590101</v>
       </c>
       <c r="B46" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5260,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>472249</v>
+        <v>472128</v>
       </c>
       <c r="R46" t="n">
-        <v>6716778</v>
+        <v>6716533</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5301,42 +5323,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133589832</v>
+        <v>133590113</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5344,10 +5361,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>472206</v>
+        <v>472116</v>
       </c>
       <c r="R47" t="n">
-        <v>6716317</v>
+        <v>6716545</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5382,17 +5399,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5411,32 +5424,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133590454</v>
+        <v>133590126</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5449,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>472220</v>
+        <v>472123</v>
       </c>
       <c r="R48" t="n">
-        <v>6716814</v>
+        <v>6716569</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5512,14 +5525,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133589949</v>
+        <v>133590135</v>
       </c>
       <c r="B49" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5550,13 +5563,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>472174</v>
+        <v>472107</v>
       </c>
       <c r="R49" t="n">
-        <v>6716377</v>
+        <v>6716575</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5613,14 +5626,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133589839</v>
+        <v>133590144</v>
       </c>
       <c r="B50" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5651,10 +5664,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>472288</v>
+        <v>472119</v>
       </c>
       <c r="R50" t="n">
-        <v>6716309</v>
+        <v>6716583</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5714,32 +5727,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133590570</v>
+        <v>133590172</v>
       </c>
       <c r="B51" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,10 +5765,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>472257</v>
+        <v>472115</v>
       </c>
       <c r="R51" t="n">
-        <v>6716771</v>
+        <v>6716620</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5815,42 +5828,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133591871</v>
+        <v>133590189</v>
       </c>
       <c r="B52" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5858,10 +5866,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>472421</v>
+        <v>472100</v>
       </c>
       <c r="R52" t="n">
-        <v>6716519</v>
+        <v>6716639</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5902,6 +5910,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5920,14 +5929,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133589557</v>
+        <v>133590202</v>
       </c>
       <c r="B53" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5958,13 +5967,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>472355</v>
+        <v>472083</v>
       </c>
       <c r="R53" t="n">
-        <v>6716306</v>
+        <v>6716615</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5988,12 +5997,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6021,14 +6030,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133590280</v>
+        <v>133590229</v>
       </c>
       <c r="B54" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6055,14 +6064,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ballthjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>472057</v>
+        <v>472048</v>
       </c>
       <c r="R54" t="n">
-        <v>6716745</v>
+        <v>6716642</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6122,14 +6131,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133589789</v>
+        <v>133590280</v>
       </c>
       <c r="B55" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6156,14 +6165,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballthjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>472223</v>
+        <v>472057</v>
       </c>
       <c r="R55" t="n">
-        <v>6716268</v>
+        <v>6716745</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6223,14 +6232,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133589660</v>
+        <v>133590286</v>
       </c>
       <c r="B56" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6261,10 +6270,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>472264</v>
+        <v>472056</v>
       </c>
       <c r="R56" t="n">
-        <v>6716238</v>
+        <v>6716776</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6324,14 +6333,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133590101</v>
+        <v>133590302</v>
       </c>
       <c r="B57" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6362,10 +6371,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>472128</v>
+        <v>472041</v>
       </c>
       <c r="R57" t="n">
-        <v>6716533</v>
+        <v>6716845</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6425,14 +6434,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133592299</v>
+        <v>133590319</v>
       </c>
       <c r="B58" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6463,10 +6472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>472393</v>
+        <v>472145</v>
       </c>
       <c r="R58" t="n">
-        <v>6716395</v>
+        <v>6716826</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6526,42 +6535,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133591759</v>
+        <v>133590480</v>
       </c>
       <c r="B59" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6569,13 +6573,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>472442</v>
+        <v>472200</v>
       </c>
       <c r="R59" t="n">
-        <v>6716568</v>
+        <v>6716786</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6613,6 +6617,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6631,14 +6636,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133589587</v>
+        <v>133590486</v>
       </c>
       <c r="B60" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6669,10 +6674,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>472365</v>
+        <v>472224</v>
       </c>
       <c r="R60" t="n">
-        <v>6716324</v>
+        <v>6716803</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6699,12 +6704,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,14 +6737,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133589426</v>
+        <v>133590494</v>
       </c>
       <c r="B61" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6770,10 +6775,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>472436</v>
+        <v>472235</v>
       </c>
       <c r="R61" t="n">
-        <v>6716208</v>
+        <v>6716801</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6800,12 +6805,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,14 +6838,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133590189</v>
+        <v>133590498</v>
       </c>
       <c r="B62" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6871,10 +6876,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>472100</v>
+        <v>472251</v>
       </c>
       <c r="R62" t="n">
-        <v>6716639</v>
+        <v>6716795</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6934,42 +6939,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133592346</v>
+        <v>133590577</v>
       </c>
       <c r="B63" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>472396</v>
+        <v>472193</v>
       </c>
       <c r="R63" t="n">
-        <v>6716339</v>
+        <v>6716740</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7015,17 +7015,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Betad tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7044,32 +7040,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133590240</v>
+        <v>133590689</v>
       </c>
       <c r="B64" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7082,13 +7078,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>472083</v>
+        <v>472273</v>
       </c>
       <c r="R64" t="n">
-        <v>6716723</v>
+        <v>6716739</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7145,32 +7141,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133591819</v>
+        <v>133591252</v>
       </c>
       <c r="B65" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7183,10 +7179,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>472431</v>
+        <v>472357</v>
       </c>
       <c r="R65" t="n">
-        <v>6716531</v>
+        <v>6716679</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7246,32 +7242,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133589444</v>
+        <v>133591302</v>
       </c>
       <c r="B66" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7284,13 +7280,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>472312</v>
+        <v>472353</v>
       </c>
       <c r="R66" t="n">
-        <v>6716221</v>
+        <v>6716653</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7314,12 +7310,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7347,32 +7343,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133590417</v>
+        <v>133591353</v>
       </c>
       <c r="B67" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7385,10 +7381,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>472173</v>
+        <v>472380</v>
       </c>
       <c r="R67" t="n">
-        <v>6716842</v>
+        <v>6716634</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7448,32 +7444,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133589629</v>
+        <v>133591463</v>
       </c>
       <c r="B68" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7486,13 +7482,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>472318</v>
+        <v>472372</v>
       </c>
       <c r="R68" t="n">
-        <v>6716281</v>
+        <v>6716600</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7516,12 +7512,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7549,42 +7545,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133589542</v>
+        <v>133591484</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7592,10 +7583,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>472359</v>
+        <v>472362</v>
       </c>
       <c r="R69" t="n">
-        <v>6716287</v>
+        <v>6716594</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7622,17 +7613,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7641,6 +7627,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7659,32 +7646,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133590624</v>
+        <v>133591503</v>
       </c>
       <c r="B70" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7697,10 +7684,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>472263</v>
+        <v>472348</v>
       </c>
       <c r="R70" t="n">
-        <v>6716734</v>
+        <v>6716596</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7760,32 +7747,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133590028</v>
+        <v>133591517</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7798,13 +7785,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>472152</v>
+        <v>472342</v>
       </c>
       <c r="R71" t="n">
-        <v>6716346</v>
+        <v>6716578</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7861,14 +7848,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133589201</v>
+        <v>133591528</v>
       </c>
       <c r="B72" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7899,13 +7886,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>472581</v>
+        <v>472337</v>
       </c>
       <c r="R72" t="n">
-        <v>6716345</v>
+        <v>6716585</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7929,12 +7916,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7962,32 +7949,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133590405</v>
+        <v>133591547</v>
       </c>
       <c r="B73" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8000,10 +7987,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>472190</v>
+        <v>472365</v>
       </c>
       <c r="R73" t="n">
-        <v>6716830</v>
+        <v>6716568</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8063,14 +8050,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133590319</v>
+        <v>133592072</v>
       </c>
       <c r="B74" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8101,10 +8088,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>472145</v>
+        <v>472386</v>
       </c>
       <c r="R74" t="n">
-        <v>6716826</v>
+        <v>6716485</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8164,14 +8151,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133590202</v>
+        <v>133592104</v>
       </c>
       <c r="B75" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8202,10 +8189,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>472083</v>
+        <v>472402</v>
       </c>
       <c r="R75" t="n">
-        <v>6716615</v>
+        <v>6716474</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8265,42 +8252,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133590013</v>
+        <v>133592117</v>
       </c>
       <c r="B76" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8308,13 +8290,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>472122</v>
+        <v>472416</v>
       </c>
       <c r="R76" t="n">
-        <v>6716329</v>
+        <v>6716458</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8346,17 +8328,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Betad tall</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8375,14 +8353,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133590498</v>
+        <v>133592130</v>
       </c>
       <c r="B77" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8413,10 +8391,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>472251</v>
+        <v>472414</v>
       </c>
       <c r="R77" t="n">
-        <v>6716795</v>
+        <v>6716446</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8476,14 +8454,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133589670</v>
+        <v>133592147</v>
       </c>
       <c r="B78" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8514,10 +8492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>472280</v>
+        <v>472401</v>
       </c>
       <c r="R78" t="n">
-        <v>6716266</v>
+        <v>6716444</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -8577,32 +8555,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133590038</v>
+        <v>133592226</v>
       </c>
       <c r="B79" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8615,10 +8593,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>472157</v>
+        <v>472366</v>
       </c>
       <c r="R79" t="n">
-        <v>6716343</v>
+        <v>6716420</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8678,14 +8656,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133589849</v>
+        <v>133592281</v>
       </c>
       <c r="B80" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8712,17 +8690,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Balltjärnen, Dlr</t>
+          <t>Ballrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>472309</v>
+        <v>472411</v>
       </c>
       <c r="R80" t="n">
-        <v>6716305</v>
+        <v>6716401</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8779,14 +8757,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133590135</v>
+        <v>133592299</v>
       </c>
       <c r="B81" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -8817,13 +8795,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>472107</v>
+        <v>472393</v>
       </c>
       <c r="R81" t="n">
-        <v>6716575</v>
+        <v>6716395</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8880,10 +8858,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133590391</v>
+        <v>133589444</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8891,31 +8869,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8923,13 +8896,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>472175</v>
+        <v>472312</v>
       </c>
       <c r="R82" t="n">
-        <v>6716830</v>
+        <v>6716221</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8953,17 +8926,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8972,6 +8940,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8990,10 +8959,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133591463</v>
+        <v>133589484</v>
       </c>
       <c r="B83" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9001,21 +8970,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9028,13 +8997,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>472372</v>
+        <v>472324</v>
       </c>
       <c r="R83" t="n">
-        <v>6716600</v>
+        <v>6716197</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9058,12 +9027,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9091,10 +9060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133591528</v>
+        <v>133589629</v>
       </c>
       <c r="B84" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9102,21 +9071,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9129,13 +9098,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>472337</v>
+        <v>472318</v>
       </c>
       <c r="R84" t="n">
-        <v>6716585</v>
+        <v>6716281</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9159,12 +9128,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9192,10 +9161,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133590113</v>
+        <v>133589761</v>
       </c>
       <c r="B85" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9203,21 +9172,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9230,10 +9199,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>472116</v>
+        <v>472217</v>
       </c>
       <c r="R85" t="n">
-        <v>6716545</v>
+        <v>6716274</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -9293,10 +9262,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133589470</v>
+        <v>133589775</v>
       </c>
       <c r="B86" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9304,21 +9273,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9331,13 +9300,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>472321</v>
+        <v>472221</v>
       </c>
       <c r="R86" t="n">
-        <v>6716236</v>
+        <v>6716291</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9361,12 +9330,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9394,10 +9363,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133589858</v>
+        <v>133589958</v>
       </c>
       <c r="B87" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9405,21 +9374,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9432,13 +9401,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>472330</v>
+        <v>472167</v>
       </c>
       <c r="R87" t="n">
-        <v>6716313</v>
+        <v>6716325</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9495,10 +9464,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133590053</v>
+        <v>133590038</v>
       </c>
       <c r="B88" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9506,21 +9475,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9533,13 +9502,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>472187</v>
+        <v>472157</v>
       </c>
       <c r="R88" t="n">
-        <v>6716406</v>
+        <v>6716343</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9596,10 +9565,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133589365</v>
+        <v>133590240</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9607,31 +9576,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9639,13 +9603,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>472559</v>
+        <v>472083</v>
       </c>
       <c r="R89" t="n">
-        <v>6716299</v>
+        <v>6716723</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9669,17 +9633,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9688,6 +9647,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9706,10 +9666,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133590229</v>
+        <v>133590308</v>
       </c>
       <c r="B90" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9717,21 +9677,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9744,10 +9704,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>472048</v>
+        <v>472127</v>
       </c>
       <c r="R90" t="n">
-        <v>6716642</v>
+        <v>6716842</v>
       </c>
       <c r="S90" t="n">
         <v>50</v>
@@ -9807,44 +9767,36 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133592016</v>
+        <v>133590405</v>
       </c>
       <c r="B91" t="n">
-        <v>93264</v>
+        <v>79130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -9853,10 +9805,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>472439</v>
+        <v>472190</v>
       </c>
       <c r="R91" t="n">
-        <v>6716486</v>
+        <v>6716830</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -9889,11 +9841,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9921,44 +9868,36 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133591328</v>
+        <v>133590417</v>
       </c>
       <c r="B92" t="n">
-        <v>93264</v>
+        <v>79130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -9967,10 +9906,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>472372</v>
+        <v>472173</v>
       </c>
       <c r="R92" t="n">
-        <v>6716649</v>
+        <v>6716842</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10003,11 +9942,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Fruktkroppar från 2025</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10035,10 +9969,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133592323</v>
+        <v>133590506</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10046,31 +9980,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10078,13 +10007,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>472392</v>
+        <v>472256</v>
       </c>
       <c r="R93" t="n">
-        <v>6716353</v>
+        <v>6716763</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10116,17 +10045,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10145,10 +10070,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133591603</v>
+        <v>133590542</v>
       </c>
       <c r="B94" t="n">
-        <v>91988</v>
+        <v>79130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10156,33 +10081,25 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -10191,13 +10108,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>472351</v>
+        <v>472247</v>
       </c>
       <c r="R94" t="n">
-        <v>6716551</v>
+        <v>6716770</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10254,10 +10171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133590506</v>
+        <v>133590549</v>
       </c>
       <c r="B95" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10292,13 +10209,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>472256</v>
+        <v>472261</v>
       </c>
       <c r="R95" t="n">
-        <v>6716763</v>
+        <v>6716776</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10355,10 +10272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133589818</v>
+        <v>133590561</v>
       </c>
       <c r="B96" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10366,31 +10283,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10398,10 +10310,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>472235</v>
+        <v>472249</v>
       </c>
       <c r="R96" t="n">
-        <v>6716289</v>
+        <v>6716778</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10436,17 +10348,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10465,10 +10373,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133590752</v>
+        <v>133590570</v>
       </c>
       <c r="B97" t="n">
-        <v>79124</v>
+        <v>79130</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10476,21 +10384,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10503,13 +10411,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>472360</v>
+        <v>472257</v>
       </c>
       <c r="R97" t="n">
-        <v>6716688</v>
+        <v>6716771</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10566,10 +10474,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133591302</v>
+        <v>133590624</v>
       </c>
       <c r="B98" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10577,21 +10485,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10604,10 +10512,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>472353</v>
+        <v>472263</v>
       </c>
       <c r="R98" t="n">
-        <v>6716653</v>
+        <v>6716734</v>
       </c>
       <c r="S98" t="n">
         <v>50</v>
@@ -10670,7 +10578,7 @@
         <v>133590632</v>
       </c>
       <c r="B99" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10768,10 +10676,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133590480</v>
+        <v>133590641</v>
       </c>
       <c r="B100" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10779,21 +10687,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10806,10 +10714,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>472200</v>
+        <v>472258</v>
       </c>
       <c r="R100" t="n">
-        <v>6716786</v>
+        <v>6716746</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10869,10 +10777,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133590286</v>
+        <v>133590674</v>
       </c>
       <c r="B101" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10880,21 +10788,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10907,10 +10815,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>472056</v>
+        <v>472291</v>
       </c>
       <c r="R101" t="n">
-        <v>6716776</v>
+        <v>6716730</v>
       </c>
       <c r="S101" t="n">
         <v>50</v>
@@ -10970,10 +10878,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133589237</v>
+        <v>133591270</v>
       </c>
       <c r="B102" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10981,21 +10889,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11008,13 +10916,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>472571</v>
+        <v>472362</v>
       </c>
       <c r="R102" t="n">
-        <v>6716309</v>
+        <v>6716669</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11038,12 +10946,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11071,10 +10979,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133589775</v>
+        <v>133591280</v>
       </c>
       <c r="B103" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11109,10 +11017,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>472221</v>
+        <v>472347</v>
       </c>
       <c r="R103" t="n">
-        <v>6716291</v>
+        <v>6716671</v>
       </c>
       <c r="S103" t="n">
         <v>50</v>
@@ -11172,56 +11080,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133591716</v>
+        <v>133591819</v>
       </c>
       <c r="B104" t="n">
-        <v>93264</v>
+        <v>79130</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ballingstjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>472427</v>
+        <v>472431</v>
       </c>
       <c r="R104" t="n">
-        <v>6716560</v>
+        <v>6716531</v>
       </c>
       <c r="S104" t="n">
         <v>50</v>
@@ -11254,11 +11154,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Från 2025</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11286,10 +11181,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133591678</v>
+        <v>133592036</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11297,31 +11192,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11329,10 +11219,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>472376</v>
+        <v>472420</v>
       </c>
       <c r="R105" t="n">
-        <v>6716608</v>
+        <v>6716488</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11367,17 +11257,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11396,10 +11282,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133589694</v>
+        <v>133592159</v>
       </c>
       <c r="B106" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11407,21 +11293,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11434,10 +11320,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>472247</v>
+        <v>472404</v>
       </c>
       <c r="R106" t="n">
-        <v>6716279</v>
+        <v>6716455</v>
       </c>
       <c r="S106" t="n">
         <v>50</v>
@@ -11497,41 +11383,40 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133590595</v>
+        <v>133589365</v>
       </c>
       <c r="B107" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -11541,10 +11426,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>472209</v>
+        <v>472559</v>
       </c>
       <c r="R107" t="n">
-        <v>6716733</v>
+        <v>6716299</v>
       </c>
       <c r="S107" t="n">
         <v>50</v>
@@ -11571,12 +11456,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11585,7 +11475,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11604,41 +11493,40 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133589998</v>
+        <v>133589542</v>
       </c>
       <c r="B108" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11648,10 +11536,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>472152</v>
+        <v>472359</v>
       </c>
       <c r="R108" t="n">
-        <v>6716323</v>
+        <v>6716287</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11678,12 +11566,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11692,7 +11585,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11711,10 +11603,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133590689</v>
+        <v>133589818</v>
       </c>
       <c r="B109" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11722,26 +11614,31 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11749,10 +11646,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>472273</v>
+        <v>472235</v>
       </c>
       <c r="R109" t="n">
-        <v>6716739</v>
+        <v>6716289</v>
       </c>
       <c r="S109" t="n">
         <v>50</v>
@@ -11787,13 +11684,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11812,10 +11713,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133590641</v>
+        <v>133589832</v>
       </c>
       <c r="B110" t="n">
-        <v>79123</v>
+        <v>57975</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11823,26 +11724,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11850,13 +11756,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>472258</v>
+        <v>472206</v>
       </c>
       <c r="R110" t="n">
-        <v>6716746</v>
+        <v>6716317</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11888,13 +11794,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11913,10 +11823,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133590172</v>
+        <v>133590160</v>
       </c>
       <c r="B111" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11924,26 +11834,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11951,13 +11866,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>472115</v>
+        <v>472090</v>
       </c>
       <c r="R111" t="n">
-        <v>6716620</v>
+        <v>6716542</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11989,13 +11904,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12014,10 +11933,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133591353</v>
+        <v>133590391</v>
       </c>
       <c r="B112" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12025,26 +11944,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12052,10 +11976,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>472380</v>
+        <v>472175</v>
       </c>
       <c r="R112" t="n">
-        <v>6716634</v>
+        <v>6716830</v>
       </c>
       <c r="S112" t="n">
         <v>50</v>
@@ -12090,13 +12014,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12115,10 +12043,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133590042</v>
+        <v>133590657</v>
       </c>
       <c r="B113" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12126,26 +12054,31 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12153,10 +12086,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>472178</v>
+        <v>472291</v>
       </c>
       <c r="R113" t="n">
-        <v>6716394</v>
+        <v>6716730</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12191,13 +12124,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12216,10 +12153,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133589154</v>
+        <v>133591432</v>
       </c>
       <c r="B114" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12227,26 +12164,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12254,13 +12196,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>472546</v>
+        <v>472381</v>
       </c>
       <c r="R114" t="n">
-        <v>6716340</v>
+        <v>6716602</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12284,21 +12226,25 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
         </is>
       </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF114" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12317,10 +12263,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133590679</v>
+        <v>133591678</v>
       </c>
       <c r="B115" t="n">
-        <v>91988</v>
+        <v>57975</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12328,34 +12274,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12363,10 +12306,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>472275</v>
+        <v>472376</v>
       </c>
       <c r="R115" t="n">
-        <v>6716740</v>
+        <v>6716608</v>
       </c>
       <c r="S115" t="n">
         <v>50</v>
@@ -12401,13 +12344,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12426,10 +12373,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133589217</v>
+        <v>133592323</v>
       </c>
       <c r="B116" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12437,26 +12384,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12464,13 +12416,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>472606</v>
+        <v>472392</v>
       </c>
       <c r="R116" t="n">
-        <v>6716343</v>
+        <v>6716353</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12494,12 +12446,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12508,7 +12465,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12527,37 +12483,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133590465</v>
+        <v>133590013</v>
       </c>
       <c r="B117" t="n">
-        <v>79124</v>
+        <v>57162</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12565,13 +12526,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>472206</v>
+        <v>472122</v>
       </c>
       <c r="R117" t="n">
-        <v>6716823</v>
+        <v>6716329</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12603,13 +12564,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12628,37 +12593,42 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133592036</v>
+        <v>133591759</v>
       </c>
       <c r="B118" t="n">
-        <v>79123</v>
+        <v>57162</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12666,10 +12636,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>472420</v>
+        <v>472442</v>
       </c>
       <c r="R118" t="n">
-        <v>6716488</v>
+        <v>6716568</v>
       </c>
       <c r="S118" t="n">
         <v>50</v>
@@ -12710,7 +12680,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12729,37 +12698,42 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133590486</v>
+        <v>133591871</v>
       </c>
       <c r="B119" t="n">
-        <v>79366</v>
+        <v>57162</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12767,13 +12741,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>472224</v>
+        <v>472421</v>
       </c>
       <c r="R119" t="n">
-        <v>6716803</v>
+        <v>6716519</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12811,7 +12785,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12830,37 +12803,42 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133591547</v>
+        <v>133592266</v>
       </c>
       <c r="B120" t="n">
-        <v>79366</v>
+        <v>57162</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12868,13 +12846,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>472365</v>
+        <v>472407</v>
       </c>
       <c r="R120" t="n">
-        <v>6716568</v>
+        <v>6716410</v>
       </c>
       <c r="S120" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12912,7 +12890,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12931,10 +12908,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133591564</v>
+        <v>133592346</v>
       </c>
       <c r="B121" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12942,30 +12919,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -12975,10 +12951,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>472366</v>
+        <v>472396</v>
       </c>
       <c r="R121" t="n">
-        <v>6716548</v>
+        <v>6716339</v>
       </c>
       <c r="S121" t="n">
         <v>50</v>
@@ -13013,13 +12989,17 @@
           <t>2026-05-03</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Betad tall.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13038,7 +13018,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133590211</v>
+        <v>133589998</v>
       </c>
       <c r="B122" t="n">
         <v>8460</v>
@@ -13082,10 +13062,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>472104</v>
+        <v>472152</v>
       </c>
       <c r="R122" t="n">
-        <v>6716608</v>
+        <v>6716323</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13145,37 +13125,43 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133589883</v>
+        <v>133590082</v>
       </c>
       <c r="B123" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13183,10 +13169,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>472271</v>
+        <v>472135</v>
       </c>
       <c r="R123" t="n">
-        <v>6716338</v>
+        <v>6716430</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13246,37 +13232,43 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133590047</v>
+        <v>133590211</v>
       </c>
       <c r="B124" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13284,13 +13276,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>472171</v>
+        <v>472104</v>
       </c>
       <c r="R124" t="n">
-        <v>6716408</v>
+        <v>6716608</v>
       </c>
       <c r="S124" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13347,40 +13339,41 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133591432</v>
+        <v>133590255</v>
       </c>
       <c r="B125" t="n">
-        <v>57975</v>
+        <v>8460</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -13390,13 +13383,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>472381</v>
+        <v>472087</v>
       </c>
       <c r="R125" t="n">
-        <v>6716602</v>
+        <v>6716742</v>
       </c>
       <c r="S125" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13428,17 +13421,13 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>4 meter upp i tall. Runt bohål 4 cm.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13457,37 +13446,43 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133590577</v>
+        <v>133590595</v>
       </c>
       <c r="B126" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13495,10 +13490,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>472193</v>
+        <v>472209</v>
       </c>
       <c r="R126" t="n">
-        <v>6716740</v>
+        <v>6716733</v>
       </c>
       <c r="S126" t="n">
         <v>50</v>
@@ -13558,7 +13553,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133591987</v>
+        <v>133591313</v>
       </c>
       <c r="B127" t="n">
         <v>8460</v>
@@ -13590,11 +13585,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13602,10 +13593,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>472419</v>
+        <v>472361</v>
       </c>
       <c r="R127" t="n">
-        <v>6716530</v>
+        <v>6716656</v>
       </c>
       <c r="S127" t="n">
         <v>50</v>
@@ -13665,37 +13656,43 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133589922</v>
+        <v>133591564</v>
       </c>
       <c r="B128" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13703,10 +13700,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>472188</v>
+        <v>472366</v>
       </c>
       <c r="R128" t="n">
-        <v>6716350</v>
+        <v>6716548</v>
       </c>
       <c r="S128" t="n">
         <v>50</v>
@@ -13766,46 +13763,43 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133589343</v>
+        <v>133591987</v>
       </c>
       <c r="B129" t="n">
-        <v>99188</v>
+        <v>8460</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13813,10 +13807,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>472584</v>
+        <v>472419</v>
       </c>
       <c r="R129" t="n">
-        <v>6716309</v>
+        <v>6716530</v>
       </c>
       <c r="S129" t="n">
         <v>50</v>
@@ -13843,12 +13837,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13876,37 +13870,43 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133590126</v>
+        <v>133592241</v>
       </c>
       <c r="B130" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>472123</v>
+        <v>472390</v>
       </c>
       <c r="R130" t="n">
-        <v>6716569</v>
+        <v>6716412</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13977,48 +13977,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133592281</v>
+        <v>133589310</v>
       </c>
       <c r="B131" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Ballrtjärnen, Dlr</t>
+          <t>Balltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>472411</v>
+        <v>472603</v>
       </c>
       <c r="R131" t="n">
-        <v>6716401</v>
+        <v>6716357</v>
       </c>
       <c r="S131" t="n">
         <v>50</v>
@@ -14045,12 +14054,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14078,42 +14087,46 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133590657</v>
+        <v>133589343</v>
       </c>
       <c r="B132" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14121,10 +14134,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>472291</v>
+        <v>472584</v>
       </c>
       <c r="R132" t="n">
-        <v>6716730</v>
+        <v>6716309</v>
       </c>
       <c r="S132" t="n">
         <v>50</v>
@@ -14151,17 +14164,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14170,6 +14178,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14188,10 +14197,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133592226</v>
+        <v>133590028</v>
       </c>
       <c r="B133" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14199,21 +14208,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14226,10 +14235,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>472366</v>
+        <v>472152</v>
       </c>
       <c r="R133" t="n">
-        <v>6716420</v>
+        <v>6716346</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14289,10 +14298,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133589604</v>
+        <v>133590454</v>
       </c>
       <c r="B134" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14300,21 +14309,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14327,10 +14336,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>472376</v>
+        <v>472220</v>
       </c>
       <c r="R134" t="n">
-        <v>6716335</v>
+        <v>6716814</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14357,12 +14366,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14390,10 +14399,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133592117</v>
+        <v>133590465</v>
       </c>
       <c r="B135" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14401,21 +14410,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14428,10 +14437,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>472416</v>
+        <v>472206</v>
       </c>
       <c r="R135" t="n">
-        <v>6716458</v>
+        <v>6716823</v>
       </c>
       <c r="S135" t="n">
         <v>50</v>
@@ -14488,6 +14497,107 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>133590752</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Balltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>472360</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6716688</v>
+      </c>
+      <c r="S136" t="n">
+        <v>25</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18713-2026 artfynd.xlsx
+++ b/artfynd/A 18713-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AZ136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591328</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592016</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1571,6 +1611,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590679</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591603</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129828593</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1987,6 +2047,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2088,6 +2153,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589139</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589154</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589182</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589217</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589237</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2694,6 +2789,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589426</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2795,6 +2895,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589470</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589509</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2997,6 +3107,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3098,6 +3213,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589587</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3199,6 +3319,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589604</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589660</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3401,6 +3531,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589670</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3502,6 +3637,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589694</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3603,6 +3743,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589715</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3704,6 +3849,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589789</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3805,6 +3955,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589839</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3906,6 +4061,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589849</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4007,6 +4167,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4108,6 +4273,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589866</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4209,6 +4379,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589876</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4310,6 +4485,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589883</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4411,6 +4591,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589886</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4512,6 +4697,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589898</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4613,6 +4803,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589911</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4714,6 +4909,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589922</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4815,6 +5015,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589936</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4916,6 +5121,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589949</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5017,6 +5227,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5118,6 +5333,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590047</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5219,6 +5439,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590053</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5320,6 +5545,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590101</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5421,6 +5651,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590113</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5522,6 +5757,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590126</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5623,6 +5863,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590135</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5724,6 +5969,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590144</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5825,6 +6075,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590172</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5926,6 +6181,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590189</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6027,6 +6287,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590202</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6128,6 +6393,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590229</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6229,6 +6499,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590280</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6330,6 +6605,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590286</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6431,6 +6711,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590302</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6532,6 +6817,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590319</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6633,6 +6923,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590480</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6734,6 +7029,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590486</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6835,6 +7135,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590494</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6936,6 +7241,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590498</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7037,6 +7347,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590577</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7138,6 +7453,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590689</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7239,6 +7559,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591252</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7340,6 +7665,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591302</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7441,6 +7771,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591353</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7542,6 +7877,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591463</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7643,6 +7983,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591484</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7744,6 +8089,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591503</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7845,6 +8195,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591517</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7946,6 +8301,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591528</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8047,6 +8407,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591547</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8148,6 +8513,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592072</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8249,6 +8619,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592104</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8350,6 +8725,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592117</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8451,6 +8831,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592130</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8552,6 +8937,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592147</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8653,6 +9043,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592226</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8754,6 +9149,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592281</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8855,6 +9255,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592299</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8956,6 +9361,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589444</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9057,6 +9467,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589484</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9158,6 +9573,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589629</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9259,6 +9679,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589761</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9360,6 +9785,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589775</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9461,6 +9891,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589958</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9562,6 +9997,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590038</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9663,6 +10103,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590240</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9764,6 +10209,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590308</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9865,6 +10315,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590405</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9966,6 +10421,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590417</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10067,6 +10527,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590506</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10168,6 +10633,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590542</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10269,6 +10739,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590549</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10370,6 +10845,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590561</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10471,6 +10951,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590570</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10572,6 +11057,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590624</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10673,6 +11163,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590632</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10774,6 +11269,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590641</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10875,6 +11375,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590674</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10976,6 +11481,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591270</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11077,6 +11587,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591280</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11178,6 +11693,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591819</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11279,6 +11799,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592036</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11380,6 +11905,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592159</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11490,6 +12020,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589365</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11600,6 +12135,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589542</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11710,6 +12250,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589818</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11820,6 +12365,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589832</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11930,6 +12480,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590160</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12040,6 +12595,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590391</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12150,6 +12710,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590657</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12260,6 +12825,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591432</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12370,6 +12940,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591678</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12480,6 +13055,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592323</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12590,6 +13170,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590013</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12695,6 +13280,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591759</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12800,6 +13390,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591871</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12905,6 +13500,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592266</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13015,6 +13615,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592346</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13122,6 +13727,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589998</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13229,6 +13839,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590082</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13336,6 +13951,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590211</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13443,6 +14063,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590255</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13550,6 +14175,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590595</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13653,6 +14283,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591313</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13760,6 +14395,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591564</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13867,6 +14507,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591987</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13974,6 +14619,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133592241</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14084,6 +14734,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589310</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14194,6 +14849,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133589343</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14295,6 +14955,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590028</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14396,6 +15061,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590454</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14497,6 +15167,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590465</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14598,8 +15273,150 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133590752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>